--- a/data/wired/policy.xlsx
+++ b/data/wired/policy.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\KT_TEST-main_BUTTONS_APPLIED\KT_TEST-main\data\wired\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8250" windowHeight="7710"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13185"/>
   </bookViews>
   <sheets>
     <sheet name="유선정책" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -203,15 +203,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -231,22 +222,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -270,12 +250,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -622,7 +596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -640,17 +614,17 @@
         <v>9</v>
       </c>
       <c r="G2" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" s="3">
         <v>0</v>
       </c>
       <c r="I2" s="4">
-        <f>G2+H2+IF(E2="Y",8,0)+IF(AND(D2="Y",F2="Y"),IF(OR(A2="I",A2="M+I",A2="U+I"),4,6),0)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <f>G2+H2+IF(E2="Y",7,0)+IF(AND(D2="Y",F2="Y"),IF(OR(A2="I",A2="M+I",A2="U+I"),4,5),0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>30</v>
       </c>
@@ -668,17 +642,17 @@
         <v>9</v>
       </c>
       <c r="G3" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H3" s="6">
         <v>0</v>
       </c>
-      <c r="I3" s="7">
-        <f t="shared" ref="I3:I5" si="0">G3+H3+IF(E3="Y",8,0)+IF(AND(D3="Y",F3="Y"),IF(OR(A3="I",A3="M+I",A3="U+I"),4,6),0)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I66" si="0">G3+H3+IF(E3="Y",7,0)+IF(AND(D3="Y",F3="Y"),IF(OR(A3="I",A3="M+I",A3="U+I"),4,5),0)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>31</v>
       </c>
@@ -696,45 +670,45 @@
         <v>9</v>
       </c>
       <c r="G4" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="6">
         <v>0</v>
       </c>
-      <c r="I4" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
+      <c r="I4" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="8">
         <v>1</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>0</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
@@ -752,17 +726,17 @@
         <v>9</v>
       </c>
       <c r="G6" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="4">
-        <f>G6+H6+IF(E6="Y",8,0)+IF(AND(D6="Y",F6="Y"),IF(OR(A6="I",A6="M+I",A6="U+I"),4,6),0)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
@@ -780,17 +754,17 @@
         <v>9</v>
       </c>
       <c r="G7" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="6">
         <v>0</v>
       </c>
-      <c r="I7" s="7">
-        <f t="shared" ref="I7:I68" si="1">G7+H7+IF(E7="Y",8,0)+IF(AND(D7="Y",F7="Y"),IF(OR(A7="I",A7="M+I",A7="U+I"),4,6),0)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I7" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
@@ -808,45 +782,45 @@
         <v>9</v>
       </c>
       <c r="G8" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="6">
         <v>0</v>
       </c>
-      <c r="I8" s="7">
-        <f t="shared" si="1"/>
-        <v>11</v>
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="C9" s="8"/>
+      <c r="D9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="9">
+      <c r="F9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="8">
         <v>1</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>0</v>
       </c>
-      <c r="I9" s="10">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I9" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -864,17 +838,17 @@
         <v>9</v>
       </c>
       <c r="G10" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H10" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I10" s="4">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
@@ -892,45 +866,45 @@
         <v>9</v>
       </c>
       <c r="G11" s="6">
+        <v>6</v>
+      </c>
+      <c r="H11" s="6">
+        <v>10</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2</v>
+      </c>
+      <c r="H12" s="8">
         <v>8</v>
       </c>
-      <c r="H11" s="6">
-        <v>13</v>
-      </c>
-      <c r="I11" s="7">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="9">
-        <v>3</v>
-      </c>
-      <c r="H12" s="9">
-        <v>10</v>
-      </c>
-      <c r="I12" s="10">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I12" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -948,17 +922,17 @@
         <v>9</v>
       </c>
       <c r="G13" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H13" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I13" s="4">
-        <f t="shared" ref="I13:I15" si="2">G13+H13+IF(E13="Y",8,0)+IF(AND(D13="Y",F13="Y"),IF(OR(A13="I",A13="M+I",A13="U+I"),4,6),0)</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -976,45 +950,45 @@
         <v>9</v>
       </c>
       <c r="G14" s="6">
+        <v>6</v>
+      </c>
+      <c r="H14" s="6">
+        <v>10</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="8">
+        <v>2</v>
+      </c>
+      <c r="H15" s="8">
         <v>8</v>
       </c>
-      <c r="H14" s="6">
-        <v>13</v>
-      </c>
-      <c r="I14" s="7">
-        <f t="shared" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="9">
-        <v>3</v>
-      </c>
-      <c r="H15" s="9">
-        <v>10</v>
-      </c>
-      <c r="I15" s="10">
-        <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I15" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
@@ -1032,17 +1006,17 @@
         <v>9</v>
       </c>
       <c r="G16" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I16" s="4">
-        <f t="shared" ref="I16:I48" si="3">G16+H16+IF(E16="Y",8,0)+IF(AND(D16="Y",F16="Y"),IF(OR(A16="I",A16="M+I",A16="U+I"),4,6),0)</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
@@ -1060,45 +1034,45 @@
         <v>9</v>
       </c>
       <c r="G17" s="6">
+        <v>6</v>
+      </c>
+      <c r="H17" s="6">
+        <v>10</v>
+      </c>
+      <c r="I17" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="8">
+        <v>2</v>
+      </c>
+      <c r="H18" s="8">
         <v>8</v>
       </c>
-      <c r="H17" s="6">
-        <v>13</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="3"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="9">
-        <v>3</v>
-      </c>
-      <c r="H18" s="9">
-        <v>10</v>
-      </c>
-      <c r="I18" s="10">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1116,17 +1090,17 @@
         <v>9</v>
       </c>
       <c r="G19" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H19" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I19" s="4">
-        <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
@@ -1144,45 +1118,45 @@
         <v>9</v>
       </c>
       <c r="G20" s="6">
+        <v>6</v>
+      </c>
+      <c r="H20" s="6">
+        <v>10</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="8">
+        <v>2</v>
+      </c>
+      <c r="H21" s="8">
         <v>8</v>
       </c>
-      <c r="H20" s="6">
-        <v>13</v>
-      </c>
-      <c r="I20" s="7">
-        <f t="shared" si="3"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="9">
-        <v>3</v>
-      </c>
-      <c r="H21" s="9">
-        <v>10</v>
-      </c>
-      <c r="I21" s="10">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I21" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1202,17 +1176,17 @@
         <v>9</v>
       </c>
       <c r="G22" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H22" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I22" s="4">
-        <f t="shared" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>17</v>
       </c>
@@ -1232,17 +1206,17 @@
         <v>9</v>
       </c>
       <c r="G23" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H23" s="6">
-        <v>12</v>
-      </c>
-      <c r="I23" s="7">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
@@ -1262,17 +1236,17 @@
         <v>9</v>
       </c>
       <c r="G24" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H24" s="6">
-        <v>12</v>
-      </c>
-      <c r="I24" s="7">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>17</v>
       </c>
@@ -1292,17 +1266,17 @@
         <v>9</v>
       </c>
       <c r="G25" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H25" s="6">
-        <v>9</v>
-      </c>
-      <c r="I25" s="7">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I25" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>17</v>
       </c>
@@ -1322,17 +1296,17 @@
         <v>9</v>
       </c>
       <c r="G26" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H26" s="6">
-        <v>5</v>
-      </c>
-      <c r="I26" s="7">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>17</v>
       </c>
@@ -1352,17 +1326,17 @@
         <v>9</v>
       </c>
       <c r="G27" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H27" s="6">
-        <v>5</v>
-      </c>
-      <c r="I27" s="7">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I27" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>17</v>
       </c>
@@ -1382,17 +1356,17 @@
         <v>9</v>
       </c>
       <c r="G28" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H28" s="6">
-        <v>9</v>
-      </c>
-      <c r="I28" s="7">
-        <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>17</v>
       </c>
@@ -1412,47 +1386,47 @@
         <v>9</v>
       </c>
       <c r="G29" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H29" s="6">
-        <v>5</v>
-      </c>
-      <c r="I29" s="7">
-        <f t="shared" si="3"/>
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="A30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="9">
+      <c r="D30" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="8">
+        <v>3</v>
+      </c>
+      <c r="H30" s="8">
         <v>4</v>
       </c>
-      <c r="H30" s="9">
-        <v>5</v>
-      </c>
-      <c r="I30" s="10">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I30" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
@@ -1472,17 +1446,17 @@
         <v>9</v>
       </c>
       <c r="G31" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H31" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I31" s="4">
-        <f t="shared" si="3"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>17</v>
       </c>
@@ -1502,17 +1476,17 @@
         <v>9</v>
       </c>
       <c r="G32" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H32" s="6">
-        <v>12</v>
-      </c>
-      <c r="I32" s="7">
-        <f t="shared" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I32" s="4">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>17</v>
       </c>
@@ -1532,17 +1506,17 @@
         <v>9</v>
       </c>
       <c r="G33" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H33" s="6">
-        <v>12</v>
-      </c>
-      <c r="I33" s="7">
-        <f t="shared" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I33" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>17</v>
       </c>
@@ -1562,17 +1536,17 @@
         <v>9</v>
       </c>
       <c r="G34" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H34" s="6">
-        <v>9</v>
-      </c>
-      <c r="I34" s="7">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>17</v>
       </c>
@@ -1592,17 +1566,17 @@
         <v>9</v>
       </c>
       <c r="G35" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H35" s="6">
-        <v>5</v>
-      </c>
-      <c r="I35" s="7">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
@@ -1622,17 +1596,17 @@
         <v>9</v>
       </c>
       <c r="G36" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H36" s="6">
-        <v>5</v>
-      </c>
-      <c r="I36" s="7">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>17</v>
       </c>
@@ -1652,17 +1626,17 @@
         <v>9</v>
       </c>
       <c r="G37" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H37" s="6">
-        <v>9</v>
-      </c>
-      <c r="I37" s="7">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>17</v>
       </c>
@@ -1682,47 +1656,47 @@
         <v>9</v>
       </c>
       <c r="G38" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H38" s="6">
-        <v>5</v>
-      </c>
-      <c r="I38" s="7">
-        <f t="shared" si="3"/>
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="9" t="s">
+      <c r="A39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="9">
+      <c r="D39" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="8">
+        <v>3</v>
+      </c>
+      <c r="H39" s="8">
         <v>4</v>
       </c>
-      <c r="H39" s="9">
-        <v>5</v>
-      </c>
-      <c r="I39" s="10">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I39" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
@@ -1742,17 +1716,17 @@
         <v>22</v>
       </c>
       <c r="G40" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H40" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I40" s="4">
-        <f t="shared" si="3"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>17</v>
       </c>
@@ -1772,17 +1746,17 @@
         <v>22</v>
       </c>
       <c r="G41" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H41" s="6">
-        <v>12</v>
-      </c>
-      <c r="I41" s="7">
-        <f t="shared" si="3"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>17</v>
       </c>
@@ -1802,17 +1776,17 @@
         <v>22</v>
       </c>
       <c r="G42" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H42" s="6">
-        <v>12</v>
-      </c>
-      <c r="I42" s="7">
-        <f t="shared" si="3"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>17</v>
       </c>
@@ -1832,17 +1806,17 @@
         <v>22</v>
       </c>
       <c r="G43" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H43" s="6">
-        <v>9</v>
-      </c>
-      <c r="I43" s="7">
-        <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I43" s="4">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>17</v>
       </c>
@@ -1862,17 +1836,17 @@
         <v>22</v>
       </c>
       <c r="G44" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H44" s="6">
-        <v>5</v>
-      </c>
-      <c r="I44" s="7">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I44" s="4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>17</v>
       </c>
@@ -1892,17 +1866,17 @@
         <v>22</v>
       </c>
       <c r="G45" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H45" s="6">
-        <v>5</v>
-      </c>
-      <c r="I45" s="7">
-        <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I45" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>17</v>
       </c>
@@ -1922,17 +1896,17 @@
         <v>22</v>
       </c>
       <c r="G46" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H46" s="6">
-        <v>9</v>
-      </c>
-      <c r="I46" s="7">
-        <f t="shared" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I46" s="4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>17</v>
       </c>
@@ -1952,47 +1926,47 @@
         <v>22</v>
       </c>
       <c r="G47" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H47" s="6">
-        <v>5</v>
-      </c>
-      <c r="I47" s="7">
-        <f t="shared" si="3"/>
-        <v>25</v>
+        <v>4</v>
+      </c>
+      <c r="I47" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="9" t="s">
+      <c r="A48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G48" s="9">
+      <c r="D48" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="8">
+        <v>3</v>
+      </c>
+      <c r="H48" s="8">
         <v>4</v>
       </c>
-      <c r="H48" s="9">
-        <v>5</v>
-      </c>
-      <c r="I48" s="10">
-        <f t="shared" si="3"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I48" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>17</v>
       </c>
@@ -2012,17 +1986,17 @@
         <v>22</v>
       </c>
       <c r="G49" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H49" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I49" s="4">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>17</v>
       </c>
@@ -2042,17 +2016,17 @@
         <v>22</v>
       </c>
       <c r="G50" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H50" s="6">
-        <v>12</v>
-      </c>
-      <c r="I50" s="7">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>17</v>
       </c>
@@ -2072,17 +2046,17 @@
         <v>22</v>
       </c>
       <c r="G51" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H51" s="6">
-        <v>12</v>
-      </c>
-      <c r="I51" s="7">
-        <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I51" s="4">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>17</v>
       </c>
@@ -2102,17 +2076,17 @@
         <v>22</v>
       </c>
       <c r="G52" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H52" s="6">
-        <v>9</v>
-      </c>
-      <c r="I52" s="7">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I52" s="4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>17</v>
       </c>
@@ -2132,17 +2106,17 @@
         <v>22</v>
       </c>
       <c r="G53" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H53" s="6">
-        <v>5</v>
-      </c>
-      <c r="I53" s="7">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I53" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>17</v>
       </c>
@@ -2162,17 +2136,17 @@
         <v>22</v>
       </c>
       <c r="G54" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H54" s="6">
-        <v>5</v>
-      </c>
-      <c r="I54" s="7">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I54" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>17</v>
       </c>
@@ -2192,17 +2166,17 @@
         <v>22</v>
       </c>
       <c r="G55" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H55" s="6">
-        <v>9</v>
-      </c>
-      <c r="I55" s="7">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I55" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>17</v>
       </c>
@@ -2222,47 +2196,47 @@
         <v>22</v>
       </c>
       <c r="G56" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H56" s="6">
-        <v>5</v>
-      </c>
-      <c r="I56" s="7">
-        <f t="shared" si="1"/>
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="I56" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="9" t="s">
+      <c r="A57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="9">
+      <c r="D57" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="8">
+        <v>3</v>
+      </c>
+      <c r="H57" s="8">
         <v>4</v>
       </c>
-      <c r="H57" s="9">
-        <v>5</v>
-      </c>
-      <c r="I57" s="10">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I57" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>26</v>
       </c>
@@ -2282,17 +2256,17 @@
         <v>9</v>
       </c>
       <c r="G58" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H58" s="3">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I58" s="4">
-        <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>26</v>
       </c>
@@ -2312,17 +2286,17 @@
         <v>9</v>
       </c>
       <c r="G59" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H59" s="6">
-        <v>40</v>
-      </c>
-      <c r="I59" s="7">
-        <f t="shared" si="1"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="I59" s="4">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>26</v>
       </c>
@@ -2342,17 +2316,17 @@
         <v>9</v>
       </c>
       <c r="G60" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H60" s="6">
-        <v>35</v>
-      </c>
-      <c r="I60" s="7">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I60" s="4">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>26</v>
       </c>
@@ -2372,17 +2346,17 @@
         <v>9</v>
       </c>
       <c r="G61" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H61" s="6">
-        <v>35</v>
-      </c>
-      <c r="I61" s="7">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I61" s="4">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>26</v>
       </c>
@@ -2402,17 +2376,17 @@
         <v>9</v>
       </c>
       <c r="G62" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H62" s="6">
-        <v>42</v>
-      </c>
-      <c r="I62" s="7">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="I62" s="4">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>26</v>
       </c>
@@ -2432,17 +2406,17 @@
         <v>9</v>
       </c>
       <c r="G63" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H63" s="6">
-        <v>35</v>
-      </c>
-      <c r="I63" s="7">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I63" s="4">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>26</v>
       </c>
@@ -2462,17 +2436,17 @@
         <v>9</v>
       </c>
       <c r="G64" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H64" s="6">
-        <v>30</v>
-      </c>
-      <c r="I64" s="7">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I64" s="4">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>26</v>
       </c>
@@ -2492,17 +2466,17 @@
         <v>9</v>
       </c>
       <c r="G65" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H65" s="6">
-        <v>30</v>
-      </c>
-      <c r="I65" s="7">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I65" s="4">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>26</v>
       </c>
@@ -2522,17 +2496,17 @@
         <v>9</v>
       </c>
       <c r="G66" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H66" s="6">
-        <v>31</v>
-      </c>
-      <c r="I66" s="7">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I66" s="4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>26</v>
       </c>
@@ -2552,47 +2526,47 @@
         <v>9</v>
       </c>
       <c r="G67" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H67" s="6">
+        <v>21</v>
+      </c>
+      <c r="I67" s="4">
+        <f t="shared" ref="I67:I130" si="1">G67+H67+IF(E67="Y",7,0)+IF(AND(D67="Y",F67="Y"),IF(OR(A67="I",A67="M+I",A67="U+I"),4,5),0)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I67" s="7">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="9" t="s">
+      <c r="B68" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D68" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G68" s="9">
-        <v>4</v>
-      </c>
-      <c r="H68" s="9">
-        <v>26</v>
-      </c>
-      <c r="I68" s="10">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D68" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="8">
+        <v>3</v>
+      </c>
+      <c r="H68" s="8">
+        <v>21</v>
+      </c>
+      <c r="I68" s="4">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>26</v>
       </c>
@@ -2612,17 +2586,17 @@
         <v>22</v>
       </c>
       <c r="G69" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H69" s="3">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I69" s="4">
-        <f t="shared" ref="I69:I79" si="4">G69+H69+IF(E69="Y",8,0)+IF(AND(D69="Y",F69="Y"),IF(OR(A69="I",A69="M+I",A69="U+I"),4,6),0)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>26</v>
       </c>
@@ -2642,17 +2616,17 @@
         <v>22</v>
       </c>
       <c r="G70" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H70" s="6">
-        <v>40</v>
-      </c>
-      <c r="I70" s="7">
-        <f t="shared" si="4"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="I70" s="4">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>26</v>
       </c>
@@ -2672,17 +2646,17 @@
         <v>22</v>
       </c>
       <c r="G71" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H71" s="6">
-        <v>35</v>
-      </c>
-      <c r="I71" s="7">
-        <f t="shared" si="4"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I71" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>26</v>
       </c>
@@ -2702,17 +2676,17 @@
         <v>22</v>
       </c>
       <c r="G72" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H72" s="6">
-        <v>35</v>
-      </c>
-      <c r="I72" s="7">
-        <f t="shared" si="4"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I72" s="4">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>26</v>
       </c>
@@ -2732,17 +2706,17 @@
         <v>22</v>
       </c>
       <c r="G73" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H73" s="6">
-        <v>42</v>
-      </c>
-      <c r="I73" s="7">
-        <f t="shared" si="4"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="I73" s="4">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>26</v>
       </c>
@@ -2762,17 +2736,17 @@
         <v>22</v>
       </c>
       <c r="G74" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H74" s="6">
-        <v>35</v>
-      </c>
-      <c r="I74" s="7">
-        <f t="shared" si="4"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I74" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>26</v>
       </c>
@@ -2792,17 +2766,17 @@
         <v>22</v>
       </c>
       <c r="G75" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H75" s="6">
-        <v>30</v>
-      </c>
-      <c r="I75" s="7">
-        <f t="shared" si="4"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I75" s="4">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>26</v>
       </c>
@@ -2822,17 +2796,17 @@
         <v>22</v>
       </c>
       <c r="G76" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H76" s="6">
-        <v>30</v>
-      </c>
-      <c r="I76" s="7">
-        <f t="shared" si="4"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I76" s="4">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>26</v>
       </c>
@@ -2852,17 +2826,17 @@
         <v>22</v>
       </c>
       <c r="G77" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H77" s="6">
-        <v>31</v>
-      </c>
-      <c r="I77" s="7">
-        <f t="shared" si="4"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I77" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>26</v>
       </c>
@@ -2882,47 +2856,47 @@
         <v>22</v>
       </c>
       <c r="G78" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6">
+        <v>21</v>
+      </c>
+      <c r="I78" s="4">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I78" s="7">
-        <f t="shared" si="4"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="9" t="s">
+      <c r="B79" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G79" s="9">
-        <v>4</v>
-      </c>
-      <c r="H79" s="9">
-        <v>26</v>
-      </c>
-      <c r="I79" s="10">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D79" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="8">
+        <v>3</v>
+      </c>
+      <c r="H79" s="8">
+        <v>21</v>
+      </c>
+      <c r="I79" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>26</v>
       </c>
@@ -2942,17 +2916,17 @@
         <v>22</v>
       </c>
       <c r="G80" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H80" s="3">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I80" s="4">
-        <f t="shared" ref="I80:I90" si="5">G80+H80+IF(E80="Y",8,0)+IF(AND(D80="Y",F80="Y"),IF(OR(A80="I",A80="M+I",A80="U+I"),4,6),0)</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>26</v>
       </c>
@@ -2972,17 +2946,17 @@
         <v>22</v>
       </c>
       <c r="G81" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H81" s="6">
-        <v>40</v>
-      </c>
-      <c r="I81" s="7">
-        <f t="shared" si="5"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="I81" s="4">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>26</v>
       </c>
@@ -3002,17 +2976,17 @@
         <v>22</v>
       </c>
       <c r="G82" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H82" s="6">
-        <v>35</v>
-      </c>
-      <c r="I82" s="7">
-        <f t="shared" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I82" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>26</v>
       </c>
@@ -3032,17 +3006,17 @@
         <v>22</v>
       </c>
       <c r="G83" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H83" s="6">
-        <v>35</v>
-      </c>
-      <c r="I83" s="7">
-        <f t="shared" si="5"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I83" s="4">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>26</v>
       </c>
@@ -3062,17 +3036,17 @@
         <v>22</v>
       </c>
       <c r="G84" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H84" s="6">
-        <v>42</v>
-      </c>
-      <c r="I84" s="7">
-        <f t="shared" si="5"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="I84" s="4">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>26</v>
       </c>
@@ -3092,17 +3066,17 @@
         <v>22</v>
       </c>
       <c r="G85" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H85" s="6">
-        <v>35</v>
-      </c>
-      <c r="I85" s="7">
-        <f t="shared" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I85" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>26</v>
       </c>
@@ -3122,17 +3096,17 @@
         <v>22</v>
       </c>
       <c r="G86" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H86" s="6">
-        <v>30</v>
-      </c>
-      <c r="I86" s="7">
-        <f t="shared" si="5"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I86" s="4">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>26</v>
       </c>
@@ -3152,17 +3126,17 @@
         <v>22</v>
       </c>
       <c r="G87" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H87" s="6">
-        <v>30</v>
-      </c>
-      <c r="I87" s="7">
-        <f t="shared" si="5"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I87" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>26</v>
       </c>
@@ -3182,17 +3156,17 @@
         <v>22</v>
       </c>
       <c r="G88" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H88" s="6">
-        <v>31</v>
-      </c>
-      <c r="I88" s="7">
-        <f t="shared" si="5"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I88" s="4">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>26</v>
       </c>
@@ -3212,47 +3186,47 @@
         <v>22</v>
       </c>
       <c r="G89" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H89" s="6">
+        <v>21</v>
+      </c>
+      <c r="I89" s="4">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I89" s="7">
-        <f t="shared" si="5"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C90" s="9" t="s">
+      <c r="B90" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D90" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E90" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G90" s="9">
-        <v>4</v>
-      </c>
-      <c r="H90" s="9">
-        <v>26</v>
-      </c>
-      <c r="I90" s="10">
-        <f t="shared" si="5"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D90" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="8">
+        <v>3</v>
+      </c>
+      <c r="H90" s="8">
+        <v>21</v>
+      </c>
+      <c r="I90" s="4">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>26</v>
       </c>
@@ -3272,17 +3246,17 @@
         <v>9</v>
       </c>
       <c r="G91" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H91" s="3">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I91" s="4">
-        <f t="shared" ref="I91:I137" si="6">G91+H91+IF(E91="Y",8,0)+IF(AND(D91="Y",F91="Y"),IF(OR(A91="I",A91="M+I",A91="U+I"),4,6),0)</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>26</v>
       </c>
@@ -3302,17 +3276,17 @@
         <v>9</v>
       </c>
       <c r="G92" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H92" s="6">
-        <v>40</v>
-      </c>
-      <c r="I92" s="7">
-        <f t="shared" si="6"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="I92" s="4">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>26</v>
       </c>
@@ -3332,17 +3306,17 @@
         <v>9</v>
       </c>
       <c r="G93" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H93" s="6">
-        <v>35</v>
-      </c>
-      <c r="I93" s="7">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I93" s="4">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>26</v>
       </c>
@@ -3362,17 +3336,17 @@
         <v>9</v>
       </c>
       <c r="G94" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H94" s="6">
-        <v>35</v>
-      </c>
-      <c r="I94" s="7">
-        <f t="shared" si="6"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I94" s="4">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>26</v>
       </c>
@@ -3392,17 +3366,17 @@
         <v>9</v>
       </c>
       <c r="G95" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H95" s="6">
-        <v>42</v>
-      </c>
-      <c r="I95" s="7">
-        <f t="shared" si="6"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="I95" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>26</v>
       </c>
@@ -3422,17 +3396,17 @@
         <v>9</v>
       </c>
       <c r="G96" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H96" s="6">
-        <v>35</v>
-      </c>
-      <c r="I96" s="7">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I96" s="4">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>26</v>
       </c>
@@ -3452,17 +3426,17 @@
         <v>9</v>
       </c>
       <c r="G97" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H97" s="6">
-        <v>30</v>
-      </c>
-      <c r="I97" s="7">
-        <f t="shared" si="6"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I97" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>26</v>
       </c>
@@ -3482,17 +3456,17 @@
         <v>9</v>
       </c>
       <c r="G98" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H98" s="6">
-        <v>30</v>
-      </c>
-      <c r="I98" s="7">
-        <f t="shared" si="6"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I98" s="4">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>26</v>
       </c>
@@ -3512,17 +3486,17 @@
         <v>9</v>
       </c>
       <c r="G99" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H99" s="6">
-        <v>31</v>
-      </c>
-      <c r="I99" s="7">
-        <f t="shared" si="6"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I99" s="4">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>26</v>
       </c>
@@ -3542,47 +3516,47 @@
         <v>9</v>
       </c>
       <c r="G100" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H100" s="6">
+        <v>21</v>
+      </c>
+      <c r="I100" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I100" s="7">
-        <f t="shared" si="6"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C101" s="9" t="s">
+      <c r="B101" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D101" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E101" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G101" s="9">
-        <v>4</v>
-      </c>
-      <c r="H101" s="9">
-        <v>26</v>
-      </c>
-      <c r="I101" s="10">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D101" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G101" s="8">
+        <v>3</v>
+      </c>
+      <c r="H101" s="8">
+        <v>21</v>
+      </c>
+      <c r="I101" s="4">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>28</v>
       </c>
@@ -3602,17 +3576,17 @@
         <v>9</v>
       </c>
       <c r="G102" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H102" s="3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I102" s="4">
-        <f t="shared" si="6"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>28</v>
       </c>
@@ -3632,17 +3606,17 @@
         <v>9</v>
       </c>
       <c r="G103" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H103" s="6">
-        <v>30</v>
-      </c>
-      <c r="I103" s="7">
-        <f t="shared" si="6"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I103" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>28</v>
       </c>
@@ -3662,17 +3636,17 @@
         <v>9</v>
       </c>
       <c r="G104" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H104" s="6">
-        <v>30</v>
-      </c>
-      <c r="I104" s="7">
-        <f t="shared" si="6"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I104" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>28</v>
       </c>
@@ -3692,17 +3666,17 @@
         <v>9</v>
       </c>
       <c r="G105" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H105" s="6">
-        <v>37</v>
-      </c>
-      <c r="I105" s="7">
-        <f t="shared" si="6"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="I105" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>28</v>
       </c>
@@ -3722,17 +3696,17 @@
         <v>9</v>
       </c>
       <c r="G106" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H106" s="6">
-        <v>25</v>
-      </c>
-      <c r="I106" s="7">
-        <f t="shared" si="6"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I106" s="4">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>28</v>
       </c>
@@ -3752,17 +3726,17 @@
         <v>9</v>
       </c>
       <c r="G107" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H107" s="6">
-        <v>25</v>
-      </c>
-      <c r="I107" s="7">
-        <f t="shared" si="6"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I107" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>28</v>
       </c>
@@ -3782,17 +3756,17 @@
         <v>9</v>
       </c>
       <c r="G108" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H108" s="6">
-        <v>26</v>
-      </c>
-      <c r="I108" s="7">
-        <f t="shared" si="6"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="I108" s="4">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>28</v>
       </c>
@@ -3812,47 +3786,47 @@
         <v>9</v>
       </c>
       <c r="G109" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H109" s="6">
-        <v>21</v>
-      </c>
-      <c r="I109" s="7">
-        <f t="shared" si="6"/>
-        <v>27</v>
+        <v>17</v>
+      </c>
+      <c r="I109" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C110" s="9" t="s">
+      <c r="A110" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D110" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E110" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G110" s="9">
-        <v>4</v>
-      </c>
-      <c r="H110" s="9">
-        <v>21</v>
-      </c>
-      <c r="I110" s="10">
-        <f t="shared" si="6"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D110" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G110" s="8">
+        <v>3</v>
+      </c>
+      <c r="H110" s="8">
+        <v>17</v>
+      </c>
+      <c r="I110" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>28</v>
       </c>
@@ -3872,17 +3846,17 @@
         <v>9</v>
       </c>
       <c r="G111" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H111" s="3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I111" s="4">
-        <f t="shared" si="6"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>28</v>
       </c>
@@ -3902,17 +3876,17 @@
         <v>9</v>
       </c>
       <c r="G112" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H112" s="6">
-        <v>30</v>
-      </c>
-      <c r="I112" s="7">
-        <f t="shared" si="6"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I112" s="4">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>28</v>
       </c>
@@ -3932,17 +3906,17 @@
         <v>9</v>
       </c>
       <c r="G113" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H113" s="6">
-        <v>30</v>
-      </c>
-      <c r="I113" s="7">
-        <f t="shared" si="6"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I113" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
         <v>28</v>
       </c>
@@ -3962,17 +3936,17 @@
         <v>9</v>
       </c>
       <c r="G114" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H114" s="6">
-        <v>37</v>
-      </c>
-      <c r="I114" s="7">
-        <f t="shared" si="6"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="I114" s="4">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
         <v>28</v>
       </c>
@@ -3992,17 +3966,17 @@
         <v>9</v>
       </c>
       <c r="G115" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H115" s="6">
-        <v>25</v>
-      </c>
-      <c r="I115" s="7">
-        <f t="shared" si="6"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I115" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
         <v>28</v>
       </c>
@@ -4022,17 +3996,17 @@
         <v>9</v>
       </c>
       <c r="G116" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H116" s="6">
-        <v>25</v>
-      </c>
-      <c r="I116" s="7">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I116" s="4">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>28</v>
       </c>
@@ -4052,17 +4026,17 @@
         <v>9</v>
       </c>
       <c r="G117" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H117" s="6">
-        <v>26</v>
-      </c>
-      <c r="I117" s="7">
-        <f t="shared" si="6"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="I117" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>28</v>
       </c>
@@ -4082,47 +4056,47 @@
         <v>9</v>
       </c>
       <c r="G118" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H118" s="6">
-        <v>21</v>
-      </c>
-      <c r="I118" s="7">
-        <f t="shared" si="6"/>
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="I118" s="4">
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B119" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" s="9" t="s">
+      <c r="A119" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D119" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E119" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G119" s="9">
-        <v>4</v>
-      </c>
-      <c r="H119" s="9">
-        <v>21</v>
-      </c>
-      <c r="I119" s="10">
-        <f t="shared" si="6"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D119" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="8">
+        <v>3</v>
+      </c>
+      <c r="H119" s="8">
+        <v>17</v>
+      </c>
+      <c r="I119" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>28</v>
       </c>
@@ -4142,17 +4116,17 @@
         <v>22</v>
       </c>
       <c r="G120" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H120" s="3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I120" s="4">
-        <f t="shared" si="6"/>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
         <v>28</v>
       </c>
@@ -4172,17 +4146,17 @@
         <v>22</v>
       </c>
       <c r="G121" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H121" s="6">
-        <v>30</v>
-      </c>
-      <c r="I121" s="7">
-        <f t="shared" si="6"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I121" s="4">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>28</v>
       </c>
@@ -4202,17 +4176,17 @@
         <v>22</v>
       </c>
       <c r="G122" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H122" s="6">
-        <v>30</v>
-      </c>
-      <c r="I122" s="7">
-        <f t="shared" si="6"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I122" s="4">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>28</v>
       </c>
@@ -4232,17 +4206,17 @@
         <v>22</v>
       </c>
       <c r="G123" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H123" s="6">
-        <v>37</v>
-      </c>
-      <c r="I123" s="7">
-        <f t="shared" si="6"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="I123" s="4">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>28</v>
       </c>
@@ -4262,17 +4236,17 @@
         <v>22</v>
       </c>
       <c r="G124" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H124" s="6">
-        <v>25</v>
-      </c>
-      <c r="I124" s="7">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I124" s="4">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>28</v>
       </c>
@@ -4292,17 +4266,17 @@
         <v>22</v>
       </c>
       <c r="G125" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H125" s="6">
-        <v>25</v>
-      </c>
-      <c r="I125" s="7">
-        <f t="shared" si="6"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I125" s="4">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>28</v>
       </c>
@@ -4322,17 +4296,17 @@
         <v>22</v>
       </c>
       <c r="G126" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H126" s="6">
-        <v>26</v>
-      </c>
-      <c r="I126" s="7">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="I126" s="4">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
         <v>28</v>
       </c>
@@ -4352,47 +4326,47 @@
         <v>22</v>
       </c>
       <c r="G127" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H127" s="6">
-        <v>21</v>
-      </c>
-      <c r="I127" s="7">
-        <f t="shared" si="6"/>
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="I127" s="4">
+        <f t="shared" si="1"/>
+        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B128" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C128" s="9" t="s">
+      <c r="A128" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D128" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E128" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G128" s="9">
-        <v>4</v>
-      </c>
-      <c r="H128" s="9">
-        <v>21</v>
-      </c>
-      <c r="I128" s="10">
-        <f t="shared" si="6"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D128" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128" s="8">
+        <v>3</v>
+      </c>
+      <c r="H128" s="8">
+        <v>17</v>
+      </c>
+      <c r="I128" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>28</v>
       </c>
@@ -4412,17 +4386,17 @@
         <v>22</v>
       </c>
       <c r="G129" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H129" s="3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I129" s="4">
-        <f t="shared" si="6"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>28</v>
       </c>
@@ -4442,17 +4416,17 @@
         <v>22</v>
       </c>
       <c r="G130" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H130" s="6">
-        <v>30</v>
-      </c>
-      <c r="I130" s="7">
-        <f t="shared" si="6"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I130" s="4">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>28</v>
       </c>
@@ -4472,17 +4446,17 @@
         <v>22</v>
       </c>
       <c r="G131" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H131" s="6">
-        <v>30</v>
-      </c>
-      <c r="I131" s="7">
-        <f t="shared" si="6"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I131" s="4">
+        <f t="shared" ref="I131:I137" si="2">G131+H131+IF(E131="Y",7,0)+IF(AND(D131="Y",F131="Y"),IF(OR(A131="I",A131="M+I",A131="U+I"),4,5),0)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>28</v>
       </c>
@@ -4502,17 +4476,17 @@
         <v>22</v>
       </c>
       <c r="G132" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H132" s="6">
-        <v>37</v>
-      </c>
-      <c r="I132" s="7">
-        <f t="shared" si="6"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="I132" s="4">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>28</v>
       </c>
@@ -4532,17 +4506,17 @@
         <v>22</v>
       </c>
       <c r="G133" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H133" s="6">
-        <v>25</v>
-      </c>
-      <c r="I133" s="7">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I133" s="4">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
         <v>28</v>
       </c>
@@ -4562,17 +4536,17 @@
         <v>22</v>
       </c>
       <c r="G134" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H134" s="6">
-        <v>25</v>
-      </c>
-      <c r="I134" s="7">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I134" s="4">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
         <v>28</v>
       </c>
@@ -4592,17 +4566,17 @@
         <v>22</v>
       </c>
       <c r="G135" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H135" s="6">
-        <v>26</v>
-      </c>
-      <c r="I135" s="7">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="I135" s="4">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>28</v>
       </c>
@@ -4622,44 +4596,44 @@
         <v>22</v>
       </c>
       <c r="G136" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H136" s="6">
-        <v>21</v>
-      </c>
-      <c r="I136" s="7">
-        <f t="shared" si="6"/>
-        <v>33</v>
+        <v>17</v>
+      </c>
+      <c r="I136" s="4">
+        <f t="shared" si="2"/>
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C137" s="9" t="s">
+      <c r="A137" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D137" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E137" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G137" s="9">
-        <v>4</v>
-      </c>
-      <c r="H137" s="9">
-        <v>21</v>
-      </c>
-      <c r="I137" s="10">
-        <f t="shared" si="6"/>
-        <v>31</v>
+      <c r="D137" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137" s="8">
+        <v>3</v>
+      </c>
+      <c r="H137" s="8">
+        <v>17</v>
+      </c>
+      <c r="I137" s="4">
+        <f t="shared" si="2"/>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/wired/policy.xlsx
+++ b/data/wired/policy.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\KT_TEST-main_BUTTONS_APPLIED\KT_TEST-main\data\wired\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13185"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="8250" windowHeight="7710"/>
   </bookViews>
   <sheets>
     <sheet name="유선정책" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -203,6 +203,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -222,11 +231,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -250,6 +270,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -596,7 +622,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -614,17 +640,17 @@
         <v>9</v>
       </c>
       <c r="G2" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" s="3">
         <v>0</v>
       </c>
       <c r="I2" s="4">
-        <f>G2+H2+IF(E2="Y",7,0)+IF(AND(D2="Y",F2="Y"),IF(OR(A2="I",A2="M+I",A2="U+I"),4,5),0)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f>G2+H2+IF(E2="Y",8,0)+IF(AND(D2="Y",F2="Y"),IF(OR(A2="I",A2="M+I",A2="U+I"),4,6),0)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>30</v>
       </c>
@@ -642,17 +668,17 @@
         <v>9</v>
       </c>
       <c r="G3" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H3" s="6">
         <v>0</v>
       </c>
-      <c r="I3" s="4">
-        <f t="shared" ref="I3:I66" si="0">G3+H3+IF(E3="Y",7,0)+IF(AND(D3="Y",F3="Y"),IF(OR(A3="I",A3="M+I",A3="U+I"),4,5),0)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I5" si="0">G3+H3+IF(E3="Y",8,0)+IF(AND(D3="Y",F3="Y"),IF(OR(A3="I",A3="M+I",A3="U+I"),4,6),0)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>31</v>
       </c>
@@ -670,45 +696,45 @@
         <v>9</v>
       </c>
       <c r="G4" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="6">
         <v>0</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="8">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="9">
         <v>1</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="9">
         <v>0</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
@@ -726,17 +752,17 @@
         <v>9</v>
       </c>
       <c r="G6" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="4">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f>G6+H6+IF(E6="Y",8,0)+IF(AND(D6="Y",F6="Y"),IF(OR(A6="I",A6="M+I",A6="U+I"),4,6),0)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
@@ -754,17 +780,17 @@
         <v>9</v>
       </c>
       <c r="G7" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H7" s="6">
         <v>0</v>
       </c>
-      <c r="I7" s="4">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I7" s="7">
+        <f t="shared" ref="I7:I68" si="1">G7+H7+IF(E7="Y",8,0)+IF(AND(D7="Y",F7="Y"),IF(OR(A7="I",A7="M+I",A7="U+I"),4,6),0)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
@@ -782,45 +808,45 @@
         <v>9</v>
       </c>
       <c r="G8" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="6">
         <v>0</v>
       </c>
-      <c r="I8" s="4">
-        <f t="shared" si="0"/>
-        <v>9</v>
+      <c r="I8" s="7">
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="8">
+      <c r="F9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="9">
         <v>1</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="9">
         <v>0</v>
       </c>
-      <c r="I9" s="4">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I9" s="10">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -838,17 +864,17 @@
         <v>9</v>
       </c>
       <c r="G10" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H10" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I10" s="4">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
@@ -866,45 +892,45 @@
         <v>9</v>
       </c>
       <c r="G11" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" s="6">
-        <v>10</v>
-      </c>
-      <c r="I11" s="4">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="8">
-        <v>2</v>
-      </c>
-      <c r="H12" s="8">
-        <v>8</v>
-      </c>
-      <c r="I12" s="4">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="9">
+        <v>3</v>
+      </c>
+      <c r="H12" s="9">
+        <v>10</v>
+      </c>
+      <c r="I12" s="10">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -922,17 +948,17 @@
         <v>9</v>
       </c>
       <c r="G13" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I13" s="4">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="I13:I15" si="2">G13+H13+IF(E13="Y",8,0)+IF(AND(D13="Y",F13="Y"),IF(OR(A13="I",A13="M+I",A13="U+I"),4,6),0)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -950,45 +976,45 @@
         <v>9</v>
       </c>
       <c r="G14" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H14" s="6">
-        <v>10</v>
-      </c>
-      <c r="I14" s="4">
-        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="B15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="8">
-        <v>2</v>
-      </c>
-      <c r="H15" s="8">
-        <v>8</v>
-      </c>
-      <c r="I15" s="4">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="9">
+        <v>3</v>
+      </c>
+      <c r="H15" s="9">
+        <v>10</v>
+      </c>
+      <c r="I15" s="10">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
@@ -1006,17 +1032,17 @@
         <v>9</v>
       </c>
       <c r="G16" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I16" s="4">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="I16:I48" si="3">G16+H16+IF(E16="Y",8,0)+IF(AND(D16="Y",F16="Y"),IF(OR(A16="I",A16="M+I",A16="U+I"),4,6),0)</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
@@ -1034,45 +1060,45 @@
         <v>9</v>
       </c>
       <c r="G17" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H17" s="6">
-        <v>10</v>
-      </c>
-      <c r="I17" s="4">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="I17" s="7">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="B18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="8">
-        <v>2</v>
-      </c>
-      <c r="H18" s="8">
-        <v>8</v>
-      </c>
-      <c r="I18" s="4">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="9">
+        <v>3</v>
+      </c>
+      <c r="H18" s="9">
+        <v>10</v>
+      </c>
+      <c r="I18" s="10">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1090,17 +1116,17 @@
         <v>9</v>
       </c>
       <c r="G19" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H19" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I19" s="4">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
@@ -1118,45 +1144,45 @@
         <v>9</v>
       </c>
       <c r="G20" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H20" s="6">
-        <v>10</v>
-      </c>
-      <c r="I20" s="4">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="I20" s="7">
+        <f t="shared" si="3"/>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="8" t="s">
+      <c r="B21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="8">
-        <v>2</v>
-      </c>
-      <c r="H21" s="8">
-        <v>8</v>
-      </c>
-      <c r="I21" s="4">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F21" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="9">
+        <v>3</v>
+      </c>
+      <c r="H21" s="9">
+        <v>10</v>
+      </c>
+      <c r="I21" s="10">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1176,17 +1202,17 @@
         <v>9</v>
       </c>
       <c r="G22" s="3">
+        <v>19</v>
+      </c>
+      <c r="H22" s="3">
         <v>16</v>
       </c>
-      <c r="H22" s="3">
-        <v>13</v>
-      </c>
       <c r="I22" s="4">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>17</v>
       </c>
@@ -1206,17 +1232,17 @@
         <v>9</v>
       </c>
       <c r="G23" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H23" s="6">
-        <v>10</v>
-      </c>
-      <c r="I23" s="4">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
@@ -1236,17 +1262,17 @@
         <v>9</v>
       </c>
       <c r="G24" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H24" s="6">
-        <v>10</v>
-      </c>
-      <c r="I24" s="4">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>17</v>
       </c>
@@ -1266,17 +1292,17 @@
         <v>9</v>
       </c>
       <c r="G25" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H25" s="6">
-        <v>7</v>
-      </c>
-      <c r="I25" s="4">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>17</v>
       </c>
@@ -1296,17 +1322,17 @@
         <v>9</v>
       </c>
       <c r="G26" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H26" s="6">
-        <v>4</v>
-      </c>
-      <c r="I26" s="4">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>17</v>
       </c>
@@ -1326,17 +1352,17 @@
         <v>9</v>
       </c>
       <c r="G27" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H27" s="6">
-        <v>4</v>
-      </c>
-      <c r="I27" s="4">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>17</v>
       </c>
@@ -1356,17 +1382,17 @@
         <v>9</v>
       </c>
       <c r="G28" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H28" s="6">
-        <v>7</v>
-      </c>
-      <c r="I28" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>17</v>
       </c>
@@ -1386,47 +1412,47 @@
         <v>9</v>
       </c>
       <c r="G29" s="6">
+        <v>6</v>
+      </c>
+      <c r="H29" s="6">
+        <v>5</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="9">
         <v>4</v>
       </c>
-      <c r="H29" s="6">
-        <v>4</v>
-      </c>
-      <c r="I29" s="4">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="8">
-        <v>3</v>
-      </c>
-      <c r="H30" s="8">
-        <v>4</v>
-      </c>
-      <c r="I30" s="4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H30" s="9">
+        <v>5</v>
+      </c>
+      <c r="I30" s="10">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
@@ -1446,17 +1472,17 @@
         <v>9</v>
       </c>
       <c r="G31" s="3">
+        <v>19</v>
+      </c>
+      <c r="H31" s="3">
         <v>16</v>
       </c>
-      <c r="H31" s="3">
-        <v>13</v>
-      </c>
       <c r="I31" s="4">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>17</v>
       </c>
@@ -1476,17 +1502,17 @@
         <v>9</v>
       </c>
       <c r="G32" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H32" s="6">
-        <v>10</v>
-      </c>
-      <c r="I32" s="4">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I32" s="7">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>17</v>
       </c>
@@ -1506,17 +1532,17 @@
         <v>9</v>
       </c>
       <c r="G33" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H33" s="6">
-        <v>10</v>
-      </c>
-      <c r="I33" s="4">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I33" s="7">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>17</v>
       </c>
@@ -1536,17 +1562,17 @@
         <v>9</v>
       </c>
       <c r="G34" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H34" s="6">
-        <v>7</v>
-      </c>
-      <c r="I34" s="4">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="I34" s="7">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>17</v>
       </c>
@@ -1566,17 +1592,17 @@
         <v>9</v>
       </c>
       <c r="G35" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H35" s="6">
-        <v>4</v>
-      </c>
-      <c r="I35" s="4">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="I35" s="7">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
@@ -1596,17 +1622,17 @@
         <v>9</v>
       </c>
       <c r="G36" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H36" s="6">
-        <v>4</v>
-      </c>
-      <c r="I36" s="4">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="I36" s="7">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>17</v>
       </c>
@@ -1626,17 +1652,17 @@
         <v>9</v>
       </c>
       <c r="G37" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H37" s="6">
-        <v>7</v>
-      </c>
-      <c r="I37" s="4">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="I37" s="7">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>17</v>
       </c>
@@ -1656,47 +1682,47 @@
         <v>9</v>
       </c>
       <c r="G38" s="6">
+        <v>6</v>
+      </c>
+      <c r="H38" s="6">
+        <v>5</v>
+      </c>
+      <c r="I38" s="7">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="9">
         <v>4</v>
       </c>
-      <c r="H38" s="6">
-        <v>4</v>
-      </c>
-      <c r="I38" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="7" t="s">
+      <c r="H39" s="9">
+        <v>5</v>
+      </c>
+      <c r="I39" s="10">
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="8">
-        <v>3</v>
-      </c>
-      <c r="H39" s="8">
-        <v>4</v>
-      </c>
-      <c r="I39" s="4">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
@@ -1716,17 +1742,17 @@
         <v>22</v>
       </c>
       <c r="G40" s="3">
+        <v>19</v>
+      </c>
+      <c r="H40" s="3">
         <v>16</v>
       </c>
-      <c r="H40" s="3">
-        <v>13</v>
-      </c>
       <c r="I40" s="4">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>17</v>
       </c>
@@ -1746,17 +1772,17 @@
         <v>22</v>
       </c>
       <c r="G41" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H41" s="6">
-        <v>10</v>
-      </c>
-      <c r="I41" s="4">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I41" s="7">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>17</v>
       </c>
@@ -1776,17 +1802,17 @@
         <v>22</v>
       </c>
       <c r="G42" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H42" s="6">
-        <v>10</v>
-      </c>
-      <c r="I42" s="4">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I42" s="7">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>17</v>
       </c>
@@ -1806,17 +1832,17 @@
         <v>22</v>
       </c>
       <c r="G43" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H43" s="6">
-        <v>7</v>
-      </c>
-      <c r="I43" s="4">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="I43" s="7">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>17</v>
       </c>
@@ -1836,17 +1862,17 @@
         <v>22</v>
       </c>
       <c r="G44" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H44" s="6">
-        <v>4</v>
-      </c>
-      <c r="I44" s="4">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="I44" s="7">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>17</v>
       </c>
@@ -1866,17 +1892,17 @@
         <v>22</v>
       </c>
       <c r="G45" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H45" s="6">
-        <v>4</v>
-      </c>
-      <c r="I45" s="4">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="I45" s="7">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>17</v>
       </c>
@@ -1896,17 +1922,17 @@
         <v>22</v>
       </c>
       <c r="G46" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H46" s="6">
-        <v>7</v>
-      </c>
-      <c r="I46" s="4">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="I46" s="7">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>17</v>
       </c>
@@ -1926,47 +1952,47 @@
         <v>22</v>
       </c>
       <c r="G47" s="6">
+        <v>6</v>
+      </c>
+      <c r="H47" s="6">
+        <v>5</v>
+      </c>
+      <c r="I47" s="7">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="9">
         <v>4</v>
       </c>
-      <c r="H47" s="6">
-        <v>4</v>
-      </c>
-      <c r="I47" s="4">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G48" s="8">
-        <v>3</v>
-      </c>
-      <c r="H48" s="8">
-        <v>4</v>
-      </c>
-      <c r="I48" s="4">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H48" s="9">
+        <v>5</v>
+      </c>
+      <c r="I48" s="10">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>17</v>
       </c>
@@ -1986,17 +2012,17 @@
         <v>22</v>
       </c>
       <c r="G49" s="3">
+        <v>19</v>
+      </c>
+      <c r="H49" s="3">
         <v>16</v>
       </c>
-      <c r="H49" s="3">
-        <v>13</v>
-      </c>
       <c r="I49" s="4">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>17</v>
       </c>
@@ -2016,17 +2042,17 @@
         <v>22</v>
       </c>
       <c r="G50" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H50" s="6">
-        <v>10</v>
-      </c>
-      <c r="I50" s="4">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I50" s="7">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
         <v>17</v>
       </c>
@@ -2046,17 +2072,17 @@
         <v>22</v>
       </c>
       <c r="G51" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H51" s="6">
-        <v>10</v>
-      </c>
-      <c r="I51" s="4">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I51" s="7">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>17</v>
       </c>
@@ -2076,17 +2102,17 @@
         <v>22</v>
       </c>
       <c r="G52" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H52" s="6">
-        <v>7</v>
-      </c>
-      <c r="I52" s="4">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="I52" s="7">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>17</v>
       </c>
@@ -2106,17 +2132,17 @@
         <v>22</v>
       </c>
       <c r="G53" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H53" s="6">
-        <v>4</v>
-      </c>
-      <c r="I53" s="4">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="I53" s="7">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>17</v>
       </c>
@@ -2136,17 +2162,17 @@
         <v>22</v>
       </c>
       <c r="G54" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H54" s="6">
-        <v>4</v>
-      </c>
-      <c r="I54" s="4">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+      <c r="I54" s="7">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>17</v>
       </c>
@@ -2166,17 +2192,17 @@
         <v>22</v>
       </c>
       <c r="G55" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H55" s="6">
-        <v>7</v>
-      </c>
-      <c r="I55" s="4">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+      <c r="I55" s="7">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>17</v>
       </c>
@@ -2196,47 +2222,47 @@
         <v>22</v>
       </c>
       <c r="G56" s="6">
+        <v>6</v>
+      </c>
+      <c r="H56" s="6">
+        <v>5</v>
+      </c>
+      <c r="I56" s="7">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="9">
         <v>4</v>
       </c>
-      <c r="H56" s="6">
-        <v>4</v>
-      </c>
-      <c r="I56" s="4">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="8">
-        <v>3</v>
-      </c>
-      <c r="H57" s="8">
-        <v>4</v>
-      </c>
-      <c r="I57" s="4">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H57" s="9">
+        <v>5</v>
+      </c>
+      <c r="I57" s="10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>26</v>
       </c>
@@ -2256,17 +2282,17 @@
         <v>9</v>
       </c>
       <c r="G58" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H58" s="3">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I58" s="4">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>26</v>
       </c>
@@ -2286,17 +2312,17 @@
         <v>9</v>
       </c>
       <c r="G59" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H59" s="6">
-        <v>32</v>
-      </c>
-      <c r="I59" s="4">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="I59" s="7">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>26</v>
       </c>
@@ -2316,17 +2342,17 @@
         <v>9</v>
       </c>
       <c r="G60" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H60" s="6">
-        <v>28</v>
-      </c>
-      <c r="I60" s="4">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I60" s="7">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>26</v>
       </c>
@@ -2346,17 +2372,17 @@
         <v>9</v>
       </c>
       <c r="G61" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H61" s="6">
-        <v>28</v>
-      </c>
-      <c r="I61" s="4">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I61" s="7">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>26</v>
       </c>
@@ -2376,17 +2402,17 @@
         <v>9</v>
       </c>
       <c r="G62" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H62" s="6">
-        <v>34</v>
-      </c>
-      <c r="I62" s="4">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="I62" s="7">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>26</v>
       </c>
@@ -2406,17 +2432,17 @@
         <v>9</v>
       </c>
       <c r="G63" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H63" s="6">
-        <v>28</v>
-      </c>
-      <c r="I63" s="4">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I63" s="7">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>26</v>
       </c>
@@ -2436,17 +2462,17 @@
         <v>9</v>
       </c>
       <c r="G64" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H64" s="6">
-        <v>24</v>
-      </c>
-      <c r="I64" s="4">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I64" s="7">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>26</v>
       </c>
@@ -2466,17 +2492,17 @@
         <v>9</v>
       </c>
       <c r="G65" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H65" s="6">
-        <v>24</v>
-      </c>
-      <c r="I65" s="4">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I65" s="7">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>26</v>
       </c>
@@ -2496,77 +2522,77 @@
         <v>9</v>
       </c>
       <c r="G66" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H66" s="6">
-        <v>25</v>
-      </c>
-      <c r="I66" s="4">
-        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="I66" s="7">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G67" s="6">
+        <v>6</v>
+      </c>
+      <c r="H67" s="6">
+        <v>26</v>
+      </c>
+      <c r="I67" s="7">
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G67" s="6">
+    <row r="68" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="9">
         <v>4</v>
       </c>
-      <c r="H67" s="6">
-        <v>21</v>
-      </c>
-      <c r="I67" s="4">
-        <f t="shared" ref="I67:I130" si="1">G67+H67+IF(E67="Y",7,0)+IF(AND(D67="Y",F67="Y"),IF(OR(A67="I",A67="M+I",A67="U+I"),4,5),0)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G68" s="8">
-        <v>3</v>
-      </c>
-      <c r="H68" s="8">
-        <v>21</v>
-      </c>
-      <c r="I68" s="4">
+      <c r="H68" s="9">
+        <v>26</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>26</v>
       </c>
@@ -2586,17 +2612,17 @@
         <v>22</v>
       </c>
       <c r="G69" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H69" s="3">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I69" s="4">
-        <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="I69:I79" si="4">G69+H69+IF(E69="Y",8,0)+IF(AND(D69="Y",F69="Y"),IF(OR(A69="I",A69="M+I",A69="U+I"),4,6),0)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>26</v>
       </c>
@@ -2616,17 +2642,17 @@
         <v>22</v>
       </c>
       <c r="G70" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H70" s="6">
-        <v>32</v>
-      </c>
-      <c r="I70" s="4">
-        <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="I70" s="7">
+        <f t="shared" si="4"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>26</v>
       </c>
@@ -2646,17 +2672,17 @@
         <v>22</v>
       </c>
       <c r="G71" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H71" s="6">
-        <v>28</v>
-      </c>
-      <c r="I71" s="4">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I71" s="7">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>26</v>
       </c>
@@ -2676,17 +2702,17 @@
         <v>22</v>
       </c>
       <c r="G72" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H72" s="6">
-        <v>28</v>
-      </c>
-      <c r="I72" s="4">
-        <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I72" s="7">
+        <f t="shared" si="4"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>26</v>
       </c>
@@ -2706,17 +2732,17 @@
         <v>22</v>
       </c>
       <c r="G73" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H73" s="6">
-        <v>34</v>
-      </c>
-      <c r="I73" s="4">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="I73" s="7">
+        <f t="shared" si="4"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>26</v>
       </c>
@@ -2736,17 +2762,17 @@
         <v>22</v>
       </c>
       <c r="G74" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H74" s="6">
-        <v>28</v>
-      </c>
-      <c r="I74" s="4">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I74" s="7">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>26</v>
       </c>
@@ -2766,17 +2792,17 @@
         <v>22</v>
       </c>
       <c r="G75" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H75" s="6">
-        <v>24</v>
-      </c>
-      <c r="I75" s="4">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I75" s="7">
+        <f t="shared" si="4"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>26</v>
       </c>
@@ -2796,17 +2822,17 @@
         <v>22</v>
       </c>
       <c r="G76" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H76" s="6">
-        <v>24</v>
-      </c>
-      <c r="I76" s="4">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I76" s="7">
+        <f t="shared" si="4"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>26</v>
       </c>
@@ -2826,17 +2852,17 @@
         <v>22</v>
       </c>
       <c r="G77" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H77" s="6">
-        <v>25</v>
-      </c>
-      <c r="I77" s="4">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="I77" s="7">
+        <f t="shared" si="4"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>26</v>
       </c>
@@ -2856,47 +2882,47 @@
         <v>22</v>
       </c>
       <c r="G78" s="6">
+        <v>6</v>
+      </c>
+      <c r="H78" s="6">
+        <v>26</v>
+      </c>
+      <c r="I78" s="7">
+        <f t="shared" si="4"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="9">
         <v>4</v>
       </c>
-      <c r="H78" s="6">
-        <v>21</v>
-      </c>
-      <c r="I78" s="4">
-        <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G79" s="8">
-        <v>3</v>
-      </c>
-      <c r="H79" s="8">
-        <v>21</v>
-      </c>
-      <c r="I79" s="4">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H79" s="9">
+        <v>26</v>
+      </c>
+      <c r="I79" s="10">
+        <f t="shared" si="4"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>26</v>
       </c>
@@ -2916,17 +2942,17 @@
         <v>22</v>
       </c>
       <c r="G80" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H80" s="3">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I80" s="4">
-        <f t="shared" si="1"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="I80:I90" si="5">G80+H80+IF(E80="Y",8,0)+IF(AND(D80="Y",F80="Y"),IF(OR(A80="I",A80="M+I",A80="U+I"),4,6),0)</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>26</v>
       </c>
@@ -2946,17 +2972,17 @@
         <v>22</v>
       </c>
       <c r="G81" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H81" s="6">
-        <v>32</v>
-      </c>
-      <c r="I81" s="4">
-        <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="I81" s="7">
+        <f t="shared" si="5"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>26</v>
       </c>
@@ -2976,17 +3002,17 @@
         <v>22</v>
       </c>
       <c r="G82" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H82" s="6">
-        <v>28</v>
-      </c>
-      <c r="I82" s="4">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I82" s="7">
+        <f t="shared" si="5"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>26</v>
       </c>
@@ -3006,17 +3032,17 @@
         <v>22</v>
       </c>
       <c r="G83" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H83" s="6">
-        <v>28</v>
-      </c>
-      <c r="I83" s="4">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I83" s="7">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>26</v>
       </c>
@@ -3036,17 +3062,17 @@
         <v>22</v>
       </c>
       <c r="G84" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H84" s="6">
-        <v>34</v>
-      </c>
-      <c r="I84" s="4">
-        <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="I84" s="7">
+        <f t="shared" si="5"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>26</v>
       </c>
@@ -3066,17 +3092,17 @@
         <v>22</v>
       </c>
       <c r="G85" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H85" s="6">
-        <v>28</v>
-      </c>
-      <c r="I85" s="4">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I85" s="7">
+        <f t="shared" si="5"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>26</v>
       </c>
@@ -3096,17 +3122,17 @@
         <v>22</v>
       </c>
       <c r="G86" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H86" s="6">
-        <v>24</v>
-      </c>
-      <c r="I86" s="4">
-        <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I86" s="7">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>26</v>
       </c>
@@ -3126,17 +3152,17 @@
         <v>22</v>
       </c>
       <c r="G87" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H87" s="6">
-        <v>24</v>
-      </c>
-      <c r="I87" s="4">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I87" s="7">
+        <f t="shared" si="5"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>26</v>
       </c>
@@ -3156,77 +3182,77 @@
         <v>22</v>
       </c>
       <c r="G88" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H88" s="6">
-        <v>25</v>
-      </c>
-      <c r="I88" s="4">
-        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="I88" s="7">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G89" s="6">
+        <v>6</v>
+      </c>
+      <c r="H89" s="6">
+        <v>26</v>
+      </c>
+      <c r="I89" s="7">
+        <f t="shared" si="5"/>
         <v>38</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G89" s="6">
+    <row r="90" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="9">
         <v>4</v>
       </c>
-      <c r="H89" s="6">
-        <v>21</v>
-      </c>
-      <c r="I89" s="4">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G90" s="8">
-        <v>3</v>
-      </c>
-      <c r="H90" s="8">
-        <v>21</v>
-      </c>
-      <c r="I90" s="4">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H90" s="9">
+        <v>26</v>
+      </c>
+      <c r="I90" s="10">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>26</v>
       </c>
@@ -3246,17 +3272,17 @@
         <v>9</v>
       </c>
       <c r="G91" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H91" s="3">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I91" s="4">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="I91:I137" si="6">G91+H91+IF(E91="Y",8,0)+IF(AND(D91="Y",F91="Y"),IF(OR(A91="I",A91="M+I",A91="U+I"),4,6),0)</f>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>26</v>
       </c>
@@ -3276,17 +3302,17 @@
         <v>9</v>
       </c>
       <c r="G92" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H92" s="6">
-        <v>32</v>
-      </c>
-      <c r="I92" s="4">
-        <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="I92" s="7">
+        <f t="shared" si="6"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>26</v>
       </c>
@@ -3306,17 +3332,17 @@
         <v>9</v>
       </c>
       <c r="G93" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H93" s="6">
-        <v>28</v>
-      </c>
-      <c r="I93" s="4">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I93" s="7">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>26</v>
       </c>
@@ -3336,17 +3362,17 @@
         <v>9</v>
       </c>
       <c r="G94" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H94" s="6">
-        <v>28</v>
-      </c>
-      <c r="I94" s="4">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I94" s="7">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>26</v>
       </c>
@@ -3366,17 +3392,17 @@
         <v>9</v>
       </c>
       <c r="G95" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H95" s="6">
-        <v>34</v>
-      </c>
-      <c r="I95" s="4">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="I95" s="7">
+        <f t="shared" si="6"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>26</v>
       </c>
@@ -3396,17 +3422,17 @@
         <v>9</v>
       </c>
       <c r="G96" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H96" s="6">
-        <v>28</v>
-      </c>
-      <c r="I96" s="4">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+      <c r="I96" s="7">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>26</v>
       </c>
@@ -3426,17 +3452,17 @@
         <v>9</v>
       </c>
       <c r="G97" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H97" s="6">
-        <v>24</v>
-      </c>
-      <c r="I97" s="4">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I97" s="7">
+        <f t="shared" si="6"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>26</v>
       </c>
@@ -3456,17 +3482,17 @@
         <v>9</v>
       </c>
       <c r="G98" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H98" s="6">
-        <v>24</v>
-      </c>
-      <c r="I98" s="4">
-        <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I98" s="7">
+        <f t="shared" si="6"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>26</v>
       </c>
@@ -3486,17 +3512,17 @@
         <v>9</v>
       </c>
       <c r="G99" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H99" s="6">
-        <v>25</v>
-      </c>
-      <c r="I99" s="4">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="I99" s="7">
+        <f t="shared" si="6"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>26</v>
       </c>
@@ -3516,47 +3542,47 @@
         <v>9</v>
       </c>
       <c r="G100" s="6">
+        <v>6</v>
+      </c>
+      <c r="H100" s="6">
+        <v>26</v>
+      </c>
+      <c r="I100" s="7">
+        <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G101" s="9">
         <v>4</v>
       </c>
-      <c r="H100" s="6">
-        <v>21</v>
-      </c>
-      <c r="I100" s="4">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D101" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G101" s="8">
-        <v>3</v>
-      </c>
-      <c r="H101" s="8">
-        <v>21</v>
-      </c>
-      <c r="I101" s="4">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H101" s="9">
+        <v>26</v>
+      </c>
+      <c r="I101" s="10">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>28</v>
       </c>
@@ -3576,17 +3602,17 @@
         <v>9</v>
       </c>
       <c r="G102" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H102" s="3">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I102" s="4">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>28</v>
       </c>
@@ -3606,17 +3632,17 @@
         <v>9</v>
       </c>
       <c r="G103" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H103" s="6">
-        <v>24</v>
-      </c>
-      <c r="I103" s="4">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I103" s="7">
+        <f t="shared" si="6"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>28</v>
       </c>
@@ -3636,17 +3662,17 @@
         <v>9</v>
       </c>
       <c r="G104" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H104" s="6">
-        <v>24</v>
-      </c>
-      <c r="I104" s="4">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I104" s="7">
+        <f t="shared" si="6"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>28</v>
       </c>
@@ -3666,17 +3692,17 @@
         <v>9</v>
       </c>
       <c r="G105" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H105" s="6">
-        <v>30</v>
-      </c>
-      <c r="I105" s="4">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="I105" s="7">
+        <f t="shared" si="6"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>28</v>
       </c>
@@ -3696,17 +3722,17 @@
         <v>9</v>
       </c>
       <c r="G106" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H106" s="6">
-        <v>20</v>
-      </c>
-      <c r="I106" s="4">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="I106" s="7">
+        <f t="shared" si="6"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>28</v>
       </c>
@@ -3726,17 +3752,17 @@
         <v>9</v>
       </c>
       <c r="G107" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H107" s="6">
-        <v>20</v>
-      </c>
-      <c r="I107" s="4">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="I107" s="7">
+        <f t="shared" si="6"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>28</v>
       </c>
@@ -3756,17 +3782,17 @@
         <v>9</v>
       </c>
       <c r="G108" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H108" s="6">
-        <v>21</v>
-      </c>
-      <c r="I108" s="4">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="I108" s="7">
+        <f t="shared" si="6"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>28</v>
       </c>
@@ -3786,47 +3812,47 @@
         <v>9</v>
       </c>
       <c r="G109" s="6">
+        <v>6</v>
+      </c>
+      <c r="H109" s="6">
+        <v>21</v>
+      </c>
+      <c r="I109" s="7">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G110" s="9">
         <v>4</v>
       </c>
-      <c r="H109" s="6">
-        <v>17</v>
-      </c>
-      <c r="I109" s="4">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B110" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G110" s="8">
-        <v>3</v>
-      </c>
-      <c r="H110" s="8">
-        <v>17</v>
-      </c>
-      <c r="I110" s="4">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H110" s="9">
+        <v>21</v>
+      </c>
+      <c r="I110" s="10">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>28</v>
       </c>
@@ -3846,17 +3872,17 @@
         <v>9</v>
       </c>
       <c r="G111" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H111" s="3">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I111" s="4">
-        <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>28</v>
       </c>
@@ -3876,17 +3902,17 @@
         <v>9</v>
       </c>
       <c r="G112" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H112" s="6">
-        <v>24</v>
-      </c>
-      <c r="I112" s="4">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I112" s="7">
+        <f t="shared" si="6"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>28</v>
       </c>
@@ -3906,17 +3932,17 @@
         <v>9</v>
       </c>
       <c r="G113" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H113" s="6">
-        <v>24</v>
-      </c>
-      <c r="I113" s="4">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I113" s="7">
+        <f t="shared" si="6"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>28</v>
       </c>
@@ -3936,17 +3962,17 @@
         <v>9</v>
       </c>
       <c r="G114" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H114" s="6">
-        <v>30</v>
-      </c>
-      <c r="I114" s="4">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="I114" s="7">
+        <f t="shared" si="6"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>28</v>
       </c>
@@ -3966,17 +3992,17 @@
         <v>9</v>
       </c>
       <c r="G115" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H115" s="6">
-        <v>20</v>
-      </c>
-      <c r="I115" s="4">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="I115" s="7">
+        <f t="shared" si="6"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
         <v>28</v>
       </c>
@@ -3996,17 +4022,17 @@
         <v>9</v>
       </c>
       <c r="G116" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H116" s="6">
-        <v>20</v>
-      </c>
-      <c r="I116" s="4">
-        <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="I116" s="7">
+        <f t="shared" si="6"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
         <v>28</v>
       </c>
@@ -4026,17 +4052,17 @@
         <v>9</v>
       </c>
       <c r="G117" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H117" s="6">
-        <v>21</v>
-      </c>
-      <c r="I117" s="4">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="I117" s="7">
+        <f t="shared" si="6"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>28</v>
       </c>
@@ -4056,47 +4082,47 @@
         <v>9</v>
       </c>
       <c r="G118" s="6">
+        <v>6</v>
+      </c>
+      <c r="H118" s="6">
+        <v>21</v>
+      </c>
+      <c r="I118" s="7">
+        <f t="shared" si="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E119" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="9">
         <v>4</v>
       </c>
-      <c r="H118" s="6">
-        <v>17</v>
-      </c>
-      <c r="I118" s="4">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D119" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E119" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F119" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G119" s="8">
-        <v>3</v>
-      </c>
-      <c r="H119" s="8">
-        <v>17</v>
-      </c>
-      <c r="I119" s="4">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H119" s="9">
+        <v>21</v>
+      </c>
+      <c r="I119" s="10">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>28</v>
       </c>
@@ -4116,17 +4142,17 @@
         <v>22</v>
       </c>
       <c r="G120" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H120" s="3">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I120" s="4">
-        <f t="shared" si="1"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>28</v>
       </c>
@@ -4146,17 +4172,17 @@
         <v>22</v>
       </c>
       <c r="G121" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H121" s="6">
-        <v>24</v>
-      </c>
-      <c r="I121" s="4">
-        <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I121" s="7">
+        <f t="shared" si="6"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>28</v>
       </c>
@@ -4176,17 +4202,17 @@
         <v>22</v>
       </c>
       <c r="G122" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H122" s="6">
-        <v>24</v>
-      </c>
-      <c r="I122" s="4">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I122" s="7">
+        <f t="shared" si="6"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>28</v>
       </c>
@@ -4206,17 +4232,17 @@
         <v>22</v>
       </c>
       <c r="G123" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H123" s="6">
-        <v>30</v>
-      </c>
-      <c r="I123" s="4">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="I123" s="7">
+        <f t="shared" si="6"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>28</v>
       </c>
@@ -4236,17 +4262,17 @@
         <v>22</v>
       </c>
       <c r="G124" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H124" s="6">
-        <v>20</v>
-      </c>
-      <c r="I124" s="4">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="I124" s="7">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>28</v>
       </c>
@@ -4266,17 +4292,17 @@
         <v>22</v>
       </c>
       <c r="G125" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H125" s="6">
-        <v>20</v>
-      </c>
-      <c r="I125" s="4">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="I125" s="7">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>28</v>
       </c>
@@ -4296,17 +4322,17 @@
         <v>22</v>
       </c>
       <c r="G126" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H126" s="6">
-        <v>21</v>
-      </c>
-      <c r="I126" s="4">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="I126" s="7">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>28</v>
       </c>
@@ -4326,47 +4352,47 @@
         <v>22</v>
       </c>
       <c r="G127" s="6">
+        <v>6</v>
+      </c>
+      <c r="H127" s="6">
+        <v>21</v>
+      </c>
+      <c r="I127" s="7">
+        <f t="shared" si="6"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128" s="9">
         <v>4</v>
       </c>
-      <c r="H127" s="6">
-        <v>17</v>
-      </c>
-      <c r="I127" s="4">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B128" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D128" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E128" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F128" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G128" s="8">
-        <v>3</v>
-      </c>
-      <c r="H128" s="8">
-        <v>17</v>
-      </c>
-      <c r="I128" s="4">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H128" s="9">
+        <v>21</v>
+      </c>
+      <c r="I128" s="10">
+        <f t="shared" si="6"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>28</v>
       </c>
@@ -4386,17 +4412,17 @@
         <v>22</v>
       </c>
       <c r="G129" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H129" s="3">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="I129" s="4">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="6"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>28</v>
       </c>
@@ -4416,17 +4442,17 @@
         <v>22</v>
       </c>
       <c r="G130" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H130" s="6">
-        <v>24</v>
-      </c>
-      <c r="I130" s="4">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I130" s="7">
+        <f t="shared" si="6"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>28</v>
       </c>
@@ -4446,17 +4472,17 @@
         <v>22</v>
       </c>
       <c r="G131" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H131" s="6">
-        <v>24</v>
-      </c>
-      <c r="I131" s="4">
-        <f t="shared" ref="I131:I137" si="2">G131+H131+IF(E131="Y",7,0)+IF(AND(D131="Y",F131="Y"),IF(OR(A131="I",A131="M+I",A131="U+I"),4,5),0)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="I131" s="7">
+        <f t="shared" si="6"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>28</v>
       </c>
@@ -4476,17 +4502,17 @@
         <v>22</v>
       </c>
       <c r="G132" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H132" s="6">
-        <v>30</v>
-      </c>
-      <c r="I132" s="4">
-        <f t="shared" si="2"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="I132" s="7">
+        <f t="shared" si="6"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>28</v>
       </c>
@@ -4506,17 +4532,17 @@
         <v>22</v>
       </c>
       <c r="G133" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H133" s="6">
-        <v>20</v>
-      </c>
-      <c r="I133" s="4">
-        <f t="shared" si="2"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="I133" s="7">
+        <f t="shared" si="6"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>28</v>
       </c>
@@ -4536,17 +4562,17 @@
         <v>22</v>
       </c>
       <c r="G134" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H134" s="6">
-        <v>20</v>
-      </c>
-      <c r="I134" s="4">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="I134" s="7">
+        <f t="shared" si="6"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>28</v>
       </c>
@@ -4566,17 +4592,17 @@
         <v>22</v>
       </c>
       <c r="G135" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H135" s="6">
-        <v>21</v>
-      </c>
-      <c r="I135" s="4">
-        <f t="shared" si="2"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="I135" s="7">
+        <f t="shared" si="6"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
         <v>28</v>
       </c>
@@ -4596,44 +4622,44 @@
         <v>22</v>
       </c>
       <c r="G136" s="6">
+        <v>6</v>
+      </c>
+      <c r="H136" s="6">
+        <v>21</v>
+      </c>
+      <c r="I136" s="7">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137" s="9">
         <v>4</v>
       </c>
-      <c r="H136" s="6">
-        <v>17</v>
-      </c>
-      <c r="I136" s="4">
-        <f t="shared" si="2"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D137" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E137" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F137" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G137" s="8">
-        <v>3</v>
-      </c>
-      <c r="H137" s="8">
-        <v>17</v>
-      </c>
-      <c r="I137" s="4">
-        <f t="shared" si="2"/>
-        <v>25</v>
+      <c r="H137" s="9">
+        <v>21</v>
+      </c>
+      <c r="I137" s="10">
+        <f t="shared" si="6"/>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/wired/policy.xlsx
+++ b/data/wired/policy.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8250" windowHeight="7710"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="8250" windowHeight="9015"/>
   </bookViews>
   <sheets>
     <sheet name="유선정책" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -203,15 +203,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -231,22 +222,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -270,12 +250,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -622,7 +596,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -640,17 +614,17 @@
         <v>9</v>
       </c>
       <c r="G2" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" s="3">
         <v>0</v>
       </c>
       <c r="I2" s="4">
-        <f>G2+H2+IF(E2="Y",8,0)+IF(AND(D2="Y",F2="Y"),IF(OR(A2="I",A2="M+I",A2="U+I"),4,6),0)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <f>G2+H2+IF(E2="Y",7,0)+IF(AND(D2="Y",F2="Y"),IF(OR(A2="I",A2="M+I",A2="U+I"),4,5),0)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>30</v>
       </c>
@@ -668,17 +642,17 @@
         <v>9</v>
       </c>
       <c r="G3" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H3" s="6">
         <v>0</v>
       </c>
-      <c r="I3" s="7">
-        <f t="shared" ref="I3:I5" si="0">G3+H3+IF(E3="Y",8,0)+IF(AND(D3="Y",F3="Y"),IF(OR(A3="I",A3="M+I",A3="U+I"),4,6),0)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I66" si="0">G3+H3+IF(E3="Y",7,0)+IF(AND(D3="Y",F3="Y"),IF(OR(A3="I",A3="M+I",A3="U+I"),4,5),0)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>31</v>
       </c>
@@ -696,45 +670,45 @@
         <v>9</v>
       </c>
       <c r="G4" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="6">
         <v>0</v>
       </c>
-      <c r="I4" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
+      <c r="I4" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="9">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="8">
         <v>1</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>0</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
@@ -752,17 +726,17 @@
         <v>9</v>
       </c>
       <c r="G6" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
       </c>
       <c r="I6" s="4">
-        <f>G6+H6+IF(E6="Y",8,0)+IF(AND(D6="Y",F6="Y"),IF(OR(A6="I",A6="M+I",A6="U+I"),4,6),0)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>30</v>
       </c>
@@ -780,17 +754,17 @@
         <v>9</v>
       </c>
       <c r="G7" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="6">
         <v>0</v>
       </c>
-      <c r="I7" s="7">
-        <f t="shared" ref="I7:I68" si="1">G7+H7+IF(E7="Y",8,0)+IF(AND(D7="Y",F7="Y"),IF(OR(A7="I",A7="M+I",A7="U+I"),4,6),0)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I7" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
@@ -808,45 +782,45 @@
         <v>9</v>
       </c>
       <c r="G8" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="6">
         <v>0</v>
       </c>
-      <c r="I8" s="7">
-        <f t="shared" si="1"/>
-        <v>11</v>
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="C9" s="8"/>
+      <c r="D9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="9">
+      <c r="F9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="8">
         <v>1</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>0</v>
       </c>
-      <c r="I9" s="10">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I9" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -864,17 +838,17 @@
         <v>9</v>
       </c>
       <c r="G10" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H10" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I10" s="4">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
@@ -892,45 +866,45 @@
         <v>9</v>
       </c>
       <c r="G11" s="6">
+        <v>6</v>
+      </c>
+      <c r="H11" s="6">
+        <v>10</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2</v>
+      </c>
+      <c r="H12" s="8">
         <v>8</v>
       </c>
-      <c r="H11" s="6">
-        <v>13</v>
-      </c>
-      <c r="I11" s="7">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="9">
-        <v>3</v>
-      </c>
-      <c r="H12" s="9">
-        <v>10</v>
-      </c>
-      <c r="I12" s="10">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I12" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -948,17 +922,17 @@
         <v>9</v>
       </c>
       <c r="G13" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H13" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I13" s="4">
-        <f t="shared" ref="I13:I15" si="2">G13+H13+IF(E13="Y",8,0)+IF(AND(D13="Y",F13="Y"),IF(OR(A13="I",A13="M+I",A13="U+I"),4,6),0)</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -976,45 +950,45 @@
         <v>9</v>
       </c>
       <c r="G14" s="6">
+        <v>6</v>
+      </c>
+      <c r="H14" s="6">
+        <v>10</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" s="8">
+        <v>2</v>
+      </c>
+      <c r="H15" s="8">
         <v>8</v>
       </c>
-      <c r="H14" s="6">
-        <v>13</v>
-      </c>
-      <c r="I14" s="7">
-        <f t="shared" si="2"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="9">
-        <v>3</v>
-      </c>
-      <c r="H15" s="9">
-        <v>10</v>
-      </c>
-      <c r="I15" s="10">
-        <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I15" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
@@ -1032,17 +1006,17 @@
         <v>9</v>
       </c>
       <c r="G16" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I16" s="4">
-        <f t="shared" ref="I16:I48" si="3">G16+H16+IF(E16="Y",8,0)+IF(AND(D16="Y",F16="Y"),IF(OR(A16="I",A16="M+I",A16="U+I"),4,6),0)</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
@@ -1060,45 +1034,45 @@
         <v>9</v>
       </c>
       <c r="G17" s="6">
+        <v>6</v>
+      </c>
+      <c r="H17" s="6">
+        <v>10</v>
+      </c>
+      <c r="I17" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="8">
+        <v>2</v>
+      </c>
+      <c r="H18" s="8">
         <v>8</v>
       </c>
-      <c r="H17" s="6">
-        <v>13</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="3"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="9">
-        <v>3</v>
-      </c>
-      <c r="H18" s="9">
-        <v>10</v>
-      </c>
-      <c r="I18" s="10">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1116,17 +1090,17 @@
         <v>9</v>
       </c>
       <c r="G19" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H19" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I19" s="4">
-        <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>25</v>
       </c>
@@ -1144,45 +1118,45 @@
         <v>9</v>
       </c>
       <c r="G20" s="6">
+        <v>6</v>
+      </c>
+      <c r="H20" s="6">
+        <v>10</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="8">
+        <v>2</v>
+      </c>
+      <c r="H21" s="8">
         <v>8</v>
       </c>
-      <c r="H20" s="6">
-        <v>13</v>
-      </c>
-      <c r="I20" s="7">
-        <f t="shared" si="3"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="9">
-        <v>3</v>
-      </c>
-      <c r="H21" s="9">
-        <v>10</v>
-      </c>
-      <c r="I21" s="10">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I21" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
@@ -1202,17 +1176,17 @@
         <v>9</v>
       </c>
       <c r="G22" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H22" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I22" s="4">
-        <f t="shared" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>17</v>
       </c>
@@ -1232,17 +1206,17 @@
         <v>9</v>
       </c>
       <c r="G23" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H23" s="6">
-        <v>12</v>
-      </c>
-      <c r="I23" s="7">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>17</v>
       </c>
@@ -1262,17 +1236,17 @@
         <v>9</v>
       </c>
       <c r="G24" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H24" s="6">
-        <v>12</v>
-      </c>
-      <c r="I24" s="7">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>17</v>
       </c>
@@ -1292,17 +1266,17 @@
         <v>9</v>
       </c>
       <c r="G25" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H25" s="6">
-        <v>9</v>
-      </c>
-      <c r="I25" s="7">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I25" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>17</v>
       </c>
@@ -1322,17 +1296,17 @@
         <v>9</v>
       </c>
       <c r="G26" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H26" s="6">
-        <v>5</v>
-      </c>
-      <c r="I26" s="7">
-        <f t="shared" si="3"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>17</v>
       </c>
@@ -1352,17 +1326,17 @@
         <v>9</v>
       </c>
       <c r="G27" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H27" s="6">
-        <v>5</v>
-      </c>
-      <c r="I27" s="7">
-        <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I27" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>17</v>
       </c>
@@ -1382,17 +1356,17 @@
         <v>9</v>
       </c>
       <c r="G28" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H28" s="6">
-        <v>9</v>
-      </c>
-      <c r="I28" s="7">
-        <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>17</v>
       </c>
@@ -1412,47 +1386,47 @@
         <v>9</v>
       </c>
       <c r="G29" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H29" s="6">
-        <v>5</v>
-      </c>
-      <c r="I29" s="7">
-        <f t="shared" si="3"/>
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="A30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G30" s="9">
+      <c r="D30" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="8">
+        <v>3</v>
+      </c>
+      <c r="H30" s="8">
         <v>4</v>
       </c>
-      <c r="H30" s="9">
-        <v>5</v>
-      </c>
-      <c r="I30" s="10">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I30" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
@@ -1472,17 +1446,17 @@
         <v>9</v>
       </c>
       <c r="G31" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H31" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I31" s="4">
-        <f t="shared" si="3"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>17</v>
       </c>
@@ -1502,17 +1476,17 @@
         <v>9</v>
       </c>
       <c r="G32" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H32" s="6">
-        <v>12</v>
-      </c>
-      <c r="I32" s="7">
-        <f t="shared" si="3"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I32" s="4">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>17</v>
       </c>
@@ -1532,17 +1506,17 @@
         <v>9</v>
       </c>
       <c r="G33" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H33" s="6">
-        <v>12</v>
-      </c>
-      <c r="I33" s="7">
-        <f t="shared" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I33" s="4">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>17</v>
       </c>
@@ -1562,17 +1536,17 @@
         <v>9</v>
       </c>
       <c r="G34" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H34" s="6">
-        <v>9</v>
-      </c>
-      <c r="I34" s="7">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>17</v>
       </c>
@@ -1592,17 +1566,17 @@
         <v>9</v>
       </c>
       <c r="G35" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H35" s="6">
-        <v>5</v>
-      </c>
-      <c r="I35" s="7">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
@@ -1622,17 +1596,17 @@
         <v>9</v>
       </c>
       <c r="G36" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H36" s="6">
-        <v>5</v>
-      </c>
-      <c r="I36" s="7">
-        <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>17</v>
       </c>
@@ -1652,17 +1626,17 @@
         <v>9</v>
       </c>
       <c r="G37" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H37" s="6">
-        <v>9</v>
-      </c>
-      <c r="I37" s="7">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>17</v>
       </c>
@@ -1682,47 +1656,47 @@
         <v>9</v>
       </c>
       <c r="G38" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H38" s="6">
-        <v>5</v>
-      </c>
-      <c r="I38" s="7">
-        <f t="shared" si="3"/>
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="9" t="s">
+      <c r="A39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="9">
+      <c r="D39" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" s="8">
+        <v>3</v>
+      </c>
+      <c r="H39" s="8">
         <v>4</v>
       </c>
-      <c r="H39" s="9">
-        <v>5</v>
-      </c>
-      <c r="I39" s="10">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I39" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>17</v>
       </c>
@@ -1742,17 +1716,17 @@
         <v>22</v>
       </c>
       <c r="G40" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H40" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I40" s="4">
-        <f t="shared" si="3"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>17</v>
       </c>
@@ -1772,17 +1746,17 @@
         <v>22</v>
       </c>
       <c r="G41" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H41" s="6">
-        <v>12</v>
-      </c>
-      <c r="I41" s="7">
-        <f t="shared" si="3"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>17</v>
       </c>
@@ -1802,17 +1776,17 @@
         <v>22</v>
       </c>
       <c r="G42" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H42" s="6">
-        <v>12</v>
-      </c>
-      <c r="I42" s="7">
-        <f t="shared" si="3"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>17</v>
       </c>
@@ -1832,17 +1806,17 @@
         <v>22</v>
       </c>
       <c r="G43" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H43" s="6">
-        <v>9</v>
-      </c>
-      <c r="I43" s="7">
-        <f t="shared" si="3"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I43" s="4">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>17</v>
       </c>
@@ -1862,17 +1836,17 @@
         <v>22</v>
       </c>
       <c r="G44" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H44" s="6">
-        <v>5</v>
-      </c>
-      <c r="I44" s="7">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I44" s="4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>17</v>
       </c>
@@ -1892,17 +1866,17 @@
         <v>22</v>
       </c>
       <c r="G45" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H45" s="6">
-        <v>5</v>
-      </c>
-      <c r="I45" s="7">
-        <f t="shared" si="3"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I45" s="4">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
         <v>17</v>
       </c>
@@ -1922,17 +1896,17 @@
         <v>22</v>
       </c>
       <c r="G46" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H46" s="6">
-        <v>9</v>
-      </c>
-      <c r="I46" s="7">
-        <f t="shared" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I46" s="4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>17</v>
       </c>
@@ -1952,47 +1926,47 @@
         <v>22</v>
       </c>
       <c r="G47" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H47" s="6">
-        <v>5</v>
-      </c>
-      <c r="I47" s="7">
-        <f t="shared" si="3"/>
-        <v>25</v>
+        <v>4</v>
+      </c>
+      <c r="I47" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="9" t="s">
+      <c r="A48" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G48" s="9">
+      <c r="D48" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="8">
+        <v>3</v>
+      </c>
+      <c r="H48" s="8">
         <v>4</v>
       </c>
-      <c r="H48" s="9">
-        <v>5</v>
-      </c>
-      <c r="I48" s="10">
-        <f t="shared" si="3"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I48" s="4">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>17</v>
       </c>
@@ -2012,17 +1986,17 @@
         <v>22</v>
       </c>
       <c r="G49" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H49" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I49" s="4">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
         <v>17</v>
       </c>
@@ -2042,17 +2016,17 @@
         <v>22</v>
       </c>
       <c r="G50" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H50" s="6">
-        <v>12</v>
-      </c>
-      <c r="I50" s="7">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>17</v>
       </c>
@@ -2072,17 +2046,17 @@
         <v>22</v>
       </c>
       <c r="G51" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H51" s="6">
-        <v>12</v>
-      </c>
-      <c r="I51" s="7">
-        <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+      <c r="I51" s="4">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
         <v>17</v>
       </c>
@@ -2102,17 +2076,17 @@
         <v>22</v>
       </c>
       <c r="G52" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H52" s="6">
-        <v>9</v>
-      </c>
-      <c r="I52" s="7">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I52" s="4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>17</v>
       </c>
@@ -2132,17 +2106,17 @@
         <v>22</v>
       </c>
       <c r="G53" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H53" s="6">
-        <v>5</v>
-      </c>
-      <c r="I53" s="7">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I53" s="4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
         <v>17</v>
       </c>
@@ -2162,17 +2136,17 @@
         <v>22</v>
       </c>
       <c r="G54" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H54" s="6">
-        <v>5</v>
-      </c>
-      <c r="I54" s="7">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="I54" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
         <v>17</v>
       </c>
@@ -2192,17 +2166,17 @@
         <v>22</v>
       </c>
       <c r="G55" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H55" s="6">
-        <v>9</v>
-      </c>
-      <c r="I55" s="7">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="I55" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
         <v>17</v>
       </c>
@@ -2222,47 +2196,47 @@
         <v>22</v>
       </c>
       <c r="G56" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H56" s="6">
-        <v>5</v>
-      </c>
-      <c r="I56" s="7">
-        <f t="shared" si="1"/>
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="I56" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="9" t="s">
+      <c r="A57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="9">
+      <c r="D57" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="8">
+        <v>3</v>
+      </c>
+      <c r="H57" s="8">
         <v>4</v>
       </c>
-      <c r="H57" s="9">
-        <v>5</v>
-      </c>
-      <c r="I57" s="10">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I57" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>26</v>
       </c>
@@ -2282,17 +2256,17 @@
         <v>9</v>
       </c>
       <c r="G58" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H58" s="3">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I58" s="4">
-        <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
         <v>26</v>
       </c>
@@ -2312,17 +2286,17 @@
         <v>9</v>
       </c>
       <c r="G59" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H59" s="6">
-        <v>40</v>
-      </c>
-      <c r="I59" s="7">
-        <f t="shared" si="1"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="I59" s="4">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
         <v>26</v>
       </c>
@@ -2342,17 +2316,17 @@
         <v>9</v>
       </c>
       <c r="G60" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H60" s="6">
-        <v>35</v>
-      </c>
-      <c r="I60" s="7">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I60" s="4">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
         <v>26</v>
       </c>
@@ -2372,17 +2346,17 @@
         <v>9</v>
       </c>
       <c r="G61" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H61" s="6">
-        <v>35</v>
-      </c>
-      <c r="I61" s="7">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I61" s="4">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
         <v>26</v>
       </c>
@@ -2402,17 +2376,17 @@
         <v>9</v>
       </c>
       <c r="G62" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H62" s="6">
-        <v>42</v>
-      </c>
-      <c r="I62" s="7">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="I62" s="4">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
         <v>26</v>
       </c>
@@ -2432,17 +2406,17 @@
         <v>9</v>
       </c>
       <c r="G63" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H63" s="6">
-        <v>35</v>
-      </c>
-      <c r="I63" s="7">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I63" s="4">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>26</v>
       </c>
@@ -2462,17 +2436,17 @@
         <v>9</v>
       </c>
       <c r="G64" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H64" s="6">
-        <v>30</v>
-      </c>
-      <c r="I64" s="7">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I64" s="4">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
         <v>26</v>
       </c>
@@ -2492,17 +2466,17 @@
         <v>9</v>
       </c>
       <c r="G65" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H65" s="6">
-        <v>30</v>
-      </c>
-      <c r="I65" s="7">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I65" s="4">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
         <v>26</v>
       </c>
@@ -2522,17 +2496,17 @@
         <v>9</v>
       </c>
       <c r="G66" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H66" s="6">
-        <v>31</v>
-      </c>
-      <c r="I66" s="7">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I66" s="4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>26</v>
       </c>
@@ -2552,47 +2526,47 @@
         <v>9</v>
       </c>
       <c r="G67" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H67" s="6">
+        <v>21</v>
+      </c>
+      <c r="I67" s="4">
+        <f t="shared" ref="I67:I130" si="1">G67+H67+IF(E67="Y",7,0)+IF(AND(D67="Y",F67="Y"),IF(OR(A67="I",A67="M+I",A67="U+I"),4,5),0)</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I67" s="7">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C68" s="9" t="s">
+      <c r="B68" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D68" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F68" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G68" s="9">
-        <v>4</v>
-      </c>
-      <c r="H68" s="9">
-        <v>26</v>
-      </c>
-      <c r="I68" s="10">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D68" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G68" s="8">
+        <v>3</v>
+      </c>
+      <c r="H68" s="8">
+        <v>21</v>
+      </c>
+      <c r="I68" s="4">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>26</v>
       </c>
@@ -2612,17 +2586,17 @@
         <v>22</v>
       </c>
       <c r="G69" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H69" s="3">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I69" s="4">
-        <f t="shared" ref="I69:I79" si="4">G69+H69+IF(E69="Y",8,0)+IF(AND(D69="Y",F69="Y"),IF(OR(A69="I",A69="M+I",A69="U+I"),4,6),0)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>26</v>
       </c>
@@ -2642,17 +2616,17 @@
         <v>22</v>
       </c>
       <c r="G70" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H70" s="6">
-        <v>40</v>
-      </c>
-      <c r="I70" s="7">
-        <f t="shared" si="4"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="I70" s="4">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
         <v>26</v>
       </c>
@@ -2672,17 +2646,17 @@
         <v>22</v>
       </c>
       <c r="G71" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H71" s="6">
-        <v>35</v>
-      </c>
-      <c r="I71" s="7">
-        <f t="shared" si="4"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I71" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
         <v>26</v>
       </c>
@@ -2702,17 +2676,17 @@
         <v>22</v>
       </c>
       <c r="G72" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H72" s="6">
-        <v>35</v>
-      </c>
-      <c r="I72" s="7">
-        <f t="shared" si="4"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I72" s="4">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
         <v>26</v>
       </c>
@@ -2732,17 +2706,17 @@
         <v>22</v>
       </c>
       <c r="G73" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H73" s="6">
-        <v>42</v>
-      </c>
-      <c r="I73" s="7">
-        <f t="shared" si="4"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="I73" s="4">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>26</v>
       </c>
@@ -2762,17 +2736,17 @@
         <v>22</v>
       </c>
       <c r="G74" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H74" s="6">
-        <v>35</v>
-      </c>
-      <c r="I74" s="7">
-        <f t="shared" si="4"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I74" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>26</v>
       </c>
@@ -2792,17 +2766,17 @@
         <v>22</v>
       </c>
       <c r="G75" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H75" s="6">
-        <v>30</v>
-      </c>
-      <c r="I75" s="7">
-        <f t="shared" si="4"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I75" s="4">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
         <v>26</v>
       </c>
@@ -2822,17 +2796,17 @@
         <v>22</v>
       </c>
       <c r="G76" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H76" s="6">
-        <v>30</v>
-      </c>
-      <c r="I76" s="7">
-        <f t="shared" si="4"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I76" s="4">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
         <v>26</v>
       </c>
@@ -2852,17 +2826,17 @@
         <v>22</v>
       </c>
       <c r="G77" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H77" s="6">
-        <v>31</v>
-      </c>
-      <c r="I77" s="7">
-        <f t="shared" si="4"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I77" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
         <v>26</v>
       </c>
@@ -2882,47 +2856,47 @@
         <v>22</v>
       </c>
       <c r="G78" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6">
+        <v>21</v>
+      </c>
+      <c r="I78" s="4">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I78" s="7">
-        <f t="shared" si="4"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" s="9" t="s">
+      <c r="B79" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G79" s="9">
-        <v>4</v>
-      </c>
-      <c r="H79" s="9">
-        <v>26</v>
-      </c>
-      <c r="I79" s="10">
-        <f t="shared" si="4"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D79" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="8">
+        <v>3</v>
+      </c>
+      <c r="H79" s="8">
+        <v>21</v>
+      </c>
+      <c r="I79" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>26</v>
       </c>
@@ -2942,17 +2916,17 @@
         <v>22</v>
       </c>
       <c r="G80" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H80" s="3">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I80" s="4">
-        <f t="shared" ref="I80:I90" si="5">G80+H80+IF(E80="Y",8,0)+IF(AND(D80="Y",F80="Y"),IF(OR(A80="I",A80="M+I",A80="U+I"),4,6),0)</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>26</v>
       </c>
@@ -2972,17 +2946,17 @@
         <v>22</v>
       </c>
       <c r="G81" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H81" s="6">
-        <v>40</v>
-      </c>
-      <c r="I81" s="7">
-        <f t="shared" si="5"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="I81" s="4">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>26</v>
       </c>
@@ -3002,17 +2976,17 @@
         <v>22</v>
       </c>
       <c r="G82" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H82" s="6">
-        <v>35</v>
-      </c>
-      <c r="I82" s="7">
-        <f t="shared" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I82" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
         <v>26</v>
       </c>
@@ -3032,17 +3006,17 @@
         <v>22</v>
       </c>
       <c r="G83" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H83" s="6">
-        <v>35</v>
-      </c>
-      <c r="I83" s="7">
-        <f t="shared" si="5"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I83" s="4">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>26</v>
       </c>
@@ -3062,17 +3036,17 @@
         <v>22</v>
       </c>
       <c r="G84" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H84" s="6">
-        <v>42</v>
-      </c>
-      <c r="I84" s="7">
-        <f t="shared" si="5"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="I84" s="4">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>26</v>
       </c>
@@ -3092,17 +3066,17 @@
         <v>22</v>
       </c>
       <c r="G85" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H85" s="6">
-        <v>35</v>
-      </c>
-      <c r="I85" s="7">
-        <f t="shared" si="5"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I85" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
         <v>26</v>
       </c>
@@ -3122,17 +3096,17 @@
         <v>22</v>
       </c>
       <c r="G86" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H86" s="6">
-        <v>30</v>
-      </c>
-      <c r="I86" s="7">
-        <f t="shared" si="5"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I86" s="4">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>26</v>
       </c>
@@ -3152,17 +3126,17 @@
         <v>22</v>
       </c>
       <c r="G87" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H87" s="6">
-        <v>30</v>
-      </c>
-      <c r="I87" s="7">
-        <f t="shared" si="5"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I87" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
         <v>26</v>
       </c>
@@ -3182,17 +3156,17 @@
         <v>22</v>
       </c>
       <c r="G88" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H88" s="6">
-        <v>31</v>
-      </c>
-      <c r="I88" s="7">
-        <f t="shared" si="5"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I88" s="4">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
         <v>26</v>
       </c>
@@ -3212,47 +3186,47 @@
         <v>22</v>
       </c>
       <c r="G89" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H89" s="6">
+        <v>21</v>
+      </c>
+      <c r="I89" s="4">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I89" s="7">
-        <f t="shared" si="5"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C90" s="9" t="s">
+      <c r="B90" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D90" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E90" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G90" s="9">
-        <v>4</v>
-      </c>
-      <c r="H90" s="9">
-        <v>26</v>
-      </c>
-      <c r="I90" s="10">
-        <f t="shared" si="5"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D90" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="8">
+        <v>3</v>
+      </c>
+      <c r="H90" s="8">
+        <v>21</v>
+      </c>
+      <c r="I90" s="4">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>26</v>
       </c>
@@ -3272,17 +3246,17 @@
         <v>9</v>
       </c>
       <c r="G91" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H91" s="3">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I91" s="4">
-        <f t="shared" ref="I91:I137" si="6">G91+H91+IF(E91="Y",8,0)+IF(AND(D91="Y",F91="Y"),IF(OR(A91="I",A91="M+I",A91="U+I"),4,6),0)</f>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>26</v>
       </c>
@@ -3302,17 +3276,17 @@
         <v>9</v>
       </c>
       <c r="G92" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H92" s="6">
-        <v>40</v>
-      </c>
-      <c r="I92" s="7">
-        <f t="shared" si="6"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="I92" s="4">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>26</v>
       </c>
@@ -3332,17 +3306,17 @@
         <v>9</v>
       </c>
       <c r="G93" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H93" s="6">
-        <v>35</v>
-      </c>
-      <c r="I93" s="7">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I93" s="4">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>26</v>
       </c>
@@ -3362,17 +3336,17 @@
         <v>9</v>
       </c>
       <c r="G94" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H94" s="6">
-        <v>35</v>
-      </c>
-      <c r="I94" s="7">
-        <f t="shared" si="6"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I94" s="4">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>26</v>
       </c>
@@ -3392,17 +3366,17 @@
         <v>9</v>
       </c>
       <c r="G95" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H95" s="6">
-        <v>42</v>
-      </c>
-      <c r="I95" s="7">
-        <f t="shared" si="6"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="I95" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
         <v>26</v>
       </c>
@@ -3422,17 +3396,17 @@
         <v>9</v>
       </c>
       <c r="G96" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H96" s="6">
-        <v>35</v>
-      </c>
-      <c r="I96" s="7">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="I96" s="4">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
         <v>26</v>
       </c>
@@ -3452,17 +3426,17 @@
         <v>9</v>
       </c>
       <c r="G97" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H97" s="6">
-        <v>30</v>
-      </c>
-      <c r="I97" s="7">
-        <f t="shared" si="6"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I97" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
         <v>26</v>
       </c>
@@ -3482,17 +3456,17 @@
         <v>9</v>
       </c>
       <c r="G98" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H98" s="6">
-        <v>30</v>
-      </c>
-      <c r="I98" s="7">
-        <f t="shared" si="6"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I98" s="4">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
         <v>26</v>
       </c>
@@ -3512,17 +3486,17 @@
         <v>9</v>
       </c>
       <c r="G99" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H99" s="6">
-        <v>31</v>
-      </c>
-      <c r="I99" s="7">
-        <f t="shared" si="6"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="I99" s="4">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
         <v>26</v>
       </c>
@@ -3542,47 +3516,47 @@
         <v>9</v>
       </c>
       <c r="G100" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H100" s="6">
+        <v>21</v>
+      </c>
+      <c r="I100" s="4">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I100" s="7">
-        <f t="shared" si="6"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B101" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C101" s="9" t="s">
+      <c r="B101" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D101" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E101" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G101" s="9">
-        <v>4</v>
-      </c>
-      <c r="H101" s="9">
-        <v>26</v>
-      </c>
-      <c r="I101" s="10">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D101" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G101" s="8">
+        <v>3</v>
+      </c>
+      <c r="H101" s="8">
+        <v>21</v>
+      </c>
+      <c r="I101" s="4">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>28</v>
       </c>
@@ -3602,17 +3576,17 @@
         <v>9</v>
       </c>
       <c r="G102" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H102" s="3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I102" s="4">
-        <f t="shared" si="6"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>28</v>
       </c>
@@ -3632,17 +3606,17 @@
         <v>9</v>
       </c>
       <c r="G103" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H103" s="6">
-        <v>30</v>
-      </c>
-      <c r="I103" s="7">
-        <f t="shared" si="6"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I103" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>28</v>
       </c>
@@ -3662,17 +3636,17 @@
         <v>9</v>
       </c>
       <c r="G104" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H104" s="6">
-        <v>30</v>
-      </c>
-      <c r="I104" s="7">
-        <f t="shared" si="6"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I104" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
         <v>28</v>
       </c>
@@ -3692,17 +3666,17 @@
         <v>9</v>
       </c>
       <c r="G105" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H105" s="6">
-        <v>37</v>
-      </c>
-      <c r="I105" s="7">
-        <f t="shared" si="6"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="I105" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>28</v>
       </c>
@@ -3722,17 +3696,17 @@
         <v>9</v>
       </c>
       <c r="G106" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H106" s="6">
-        <v>25</v>
-      </c>
-      <c r="I106" s="7">
-        <f t="shared" si="6"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I106" s="4">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>28</v>
       </c>
@@ -3752,17 +3726,17 @@
         <v>9</v>
       </c>
       <c r="G107" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H107" s="6">
-        <v>25</v>
-      </c>
-      <c r="I107" s="7">
-        <f t="shared" si="6"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I107" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
         <v>28</v>
       </c>
@@ -3782,17 +3756,17 @@
         <v>9</v>
       </c>
       <c r="G108" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H108" s="6">
-        <v>26</v>
-      </c>
-      <c r="I108" s="7">
-        <f t="shared" si="6"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="I108" s="4">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
         <v>28</v>
       </c>
@@ -3812,47 +3786,47 @@
         <v>9</v>
       </c>
       <c r="G109" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H109" s="6">
-        <v>21</v>
-      </c>
-      <c r="I109" s="7">
-        <f t="shared" si="6"/>
-        <v>27</v>
+        <v>17</v>
+      </c>
+      <c r="I109" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B110" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C110" s="9" t="s">
+      <c r="A110" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D110" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E110" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G110" s="9">
-        <v>4</v>
-      </c>
-      <c r="H110" s="9">
-        <v>21</v>
-      </c>
-      <c r="I110" s="10">
-        <f t="shared" si="6"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D110" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G110" s="8">
+        <v>3</v>
+      </c>
+      <c r="H110" s="8">
+        <v>17</v>
+      </c>
+      <c r="I110" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>28</v>
       </c>
@@ -3872,17 +3846,17 @@
         <v>9</v>
       </c>
       <c r="G111" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H111" s="3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I111" s="4">
-        <f t="shared" si="6"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>28</v>
       </c>
@@ -3902,17 +3876,17 @@
         <v>9</v>
       </c>
       <c r="G112" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H112" s="6">
-        <v>30</v>
-      </c>
-      <c r="I112" s="7">
-        <f t="shared" si="6"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I112" s="4">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>28</v>
       </c>
@@ -3932,17 +3906,17 @@
         <v>9</v>
       </c>
       <c r="G113" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H113" s="6">
-        <v>30</v>
-      </c>
-      <c r="I113" s="7">
-        <f t="shared" si="6"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I113" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
         <v>28</v>
       </c>
@@ -3962,17 +3936,17 @@
         <v>9</v>
       </c>
       <c r="G114" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H114" s="6">
-        <v>37</v>
-      </c>
-      <c r="I114" s="7">
-        <f t="shared" si="6"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="I114" s="4">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
         <v>28</v>
       </c>
@@ -3992,17 +3966,17 @@
         <v>9</v>
       </c>
       <c r="G115" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H115" s="6">
-        <v>25</v>
-      </c>
-      <c r="I115" s="7">
-        <f t="shared" si="6"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I115" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="5" t="s">
         <v>28</v>
       </c>
@@ -4022,17 +3996,17 @@
         <v>9</v>
       </c>
       <c r="G116" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H116" s="6">
-        <v>25</v>
-      </c>
-      <c r="I116" s="7">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I116" s="4">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
         <v>28</v>
       </c>
@@ -4052,17 +4026,17 @@
         <v>9</v>
       </c>
       <c r="G117" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H117" s="6">
-        <v>26</v>
-      </c>
-      <c r="I117" s="7">
-        <f t="shared" si="6"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="I117" s="4">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="5" t="s">
         <v>28</v>
       </c>
@@ -4082,47 +4056,47 @@
         <v>9</v>
       </c>
       <c r="G118" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H118" s="6">
-        <v>21</v>
-      </c>
-      <c r="I118" s="7">
-        <f t="shared" si="6"/>
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="I118" s="4">
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B119" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" s="9" t="s">
+      <c r="A119" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D119" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E119" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G119" s="9">
-        <v>4</v>
-      </c>
-      <c r="H119" s="9">
-        <v>21</v>
-      </c>
-      <c r="I119" s="10">
-        <f t="shared" si="6"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D119" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="8">
+        <v>3</v>
+      </c>
+      <c r="H119" s="8">
+        <v>17</v>
+      </c>
+      <c r="I119" s="4">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>28</v>
       </c>
@@ -4142,17 +4116,17 @@
         <v>22</v>
       </c>
       <c r="G120" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H120" s="3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I120" s="4">
-        <f t="shared" si="6"/>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
         <v>28</v>
       </c>
@@ -4172,17 +4146,17 @@
         <v>22</v>
       </c>
       <c r="G121" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H121" s="6">
-        <v>30</v>
-      </c>
-      <c r="I121" s="7">
-        <f t="shared" si="6"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I121" s="4">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>28</v>
       </c>
@@ -4202,17 +4176,17 @@
         <v>22</v>
       </c>
       <c r="G122" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H122" s="6">
-        <v>30</v>
-      </c>
-      <c r="I122" s="7">
-        <f t="shared" si="6"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I122" s="4">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>28</v>
       </c>
@@ -4232,17 +4206,17 @@
         <v>22</v>
       </c>
       <c r="G123" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H123" s="6">
-        <v>37</v>
-      </c>
-      <c r="I123" s="7">
-        <f t="shared" si="6"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="I123" s="4">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
         <v>28</v>
       </c>
@@ -4262,17 +4236,17 @@
         <v>22</v>
       </c>
       <c r="G124" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H124" s="6">
-        <v>25</v>
-      </c>
-      <c r="I124" s="7">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I124" s="4">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>28</v>
       </c>
@@ -4292,17 +4266,17 @@
         <v>22</v>
       </c>
       <c r="G125" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H125" s="6">
-        <v>25</v>
-      </c>
-      <c r="I125" s="7">
-        <f t="shared" si="6"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I125" s="4">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>28</v>
       </c>
@@ -4322,17 +4296,17 @@
         <v>22</v>
       </c>
       <c r="G126" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H126" s="6">
-        <v>26</v>
-      </c>
-      <c r="I126" s="7">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="I126" s="4">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
         <v>28</v>
       </c>
@@ -4352,47 +4326,47 @@
         <v>22</v>
       </c>
       <c r="G127" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H127" s="6">
-        <v>21</v>
-      </c>
-      <c r="I127" s="7">
-        <f t="shared" si="6"/>
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="I127" s="4">
+        <f t="shared" si="1"/>
+        <v>33</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B128" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C128" s="9" t="s">
+      <c r="A128" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D128" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E128" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G128" s="9">
-        <v>4</v>
-      </c>
-      <c r="H128" s="9">
-        <v>21</v>
-      </c>
-      <c r="I128" s="10">
-        <f t="shared" si="6"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D128" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128" s="8">
+        <v>3</v>
+      </c>
+      <c r="H128" s="8">
+        <v>17</v>
+      </c>
+      <c r="I128" s="4">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>28</v>
       </c>
@@ -4412,17 +4386,17 @@
         <v>22</v>
       </c>
       <c r="G129" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H129" s="3">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I129" s="4">
-        <f t="shared" si="6"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>28</v>
       </c>
@@ -4442,17 +4416,17 @@
         <v>22</v>
       </c>
       <c r="G130" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H130" s="6">
-        <v>30</v>
-      </c>
-      <c r="I130" s="7">
-        <f t="shared" si="6"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I130" s="4">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>28</v>
       </c>
@@ -4472,17 +4446,17 @@
         <v>22</v>
       </c>
       <c r="G131" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H131" s="6">
-        <v>30</v>
-      </c>
-      <c r="I131" s="7">
-        <f t="shared" si="6"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="I131" s="4">
+        <f t="shared" ref="I131:I137" si="2">G131+H131+IF(E131="Y",7,0)+IF(AND(D131="Y",F131="Y"),IF(OR(A131="I",A131="M+I",A131="U+I"),4,5),0)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>28</v>
       </c>
@@ -4502,17 +4476,17 @@
         <v>22</v>
       </c>
       <c r="G132" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H132" s="6">
-        <v>37</v>
-      </c>
-      <c r="I132" s="7">
-        <f t="shared" si="6"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="I132" s="4">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>28</v>
       </c>
@@ -4532,17 +4506,17 @@
         <v>22</v>
       </c>
       <c r="G133" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H133" s="6">
-        <v>25</v>
-      </c>
-      <c r="I133" s="7">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I133" s="4">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
         <v>28</v>
       </c>
@@ -4562,17 +4536,17 @@
         <v>22</v>
       </c>
       <c r="G134" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H134" s="6">
-        <v>25</v>
-      </c>
-      <c r="I134" s="7">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="I134" s="4">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
         <v>28</v>
       </c>
@@ -4592,17 +4566,17 @@
         <v>22</v>
       </c>
       <c r="G135" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H135" s="6">
-        <v>26</v>
-      </c>
-      <c r="I135" s="7">
-        <f t="shared" si="6"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="I135" s="4">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
         <v>28</v>
       </c>
@@ -4622,44 +4596,44 @@
         <v>22</v>
       </c>
       <c r="G136" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H136" s="6">
-        <v>21</v>
-      </c>
-      <c r="I136" s="7">
-        <f t="shared" si="6"/>
-        <v>33</v>
+        <v>17</v>
+      </c>
+      <c r="I136" s="4">
+        <f t="shared" si="2"/>
+        <v>26</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B137" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C137" s="9" t="s">
+      <c r="A137" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D137" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E137" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F137" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G137" s="9">
-        <v>4</v>
-      </c>
-      <c r="H137" s="9">
-        <v>21</v>
-      </c>
-      <c r="I137" s="10">
-        <f t="shared" si="6"/>
-        <v>31</v>
+      <c r="D137" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137" s="8">
+        <v>3</v>
+      </c>
+      <c r="H137" s="8">
+        <v>17</v>
+      </c>
+      <c r="I137" s="4">
+        <f t="shared" si="2"/>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
